--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>1772729</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>3.64599990844727</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>3.57800006866455</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>3.56200003623962</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -62897,7 +62897,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="D2719" t="n">
-        <v>3.57800006866455</v>
+        <v>3.56200003623962</v>
       </c>
       <c r="E2719" t="n">
         <v>3.64000010490417</v>
@@ -62906,6 +62906,29 @@
         <v>3.56200003623962</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1952231</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>3.58599996566772</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>3.51200008392334</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>3.57800006866455</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>2390492</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>3.58400011062622</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>3.59599995613098</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>2715451</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>3.71199989318848</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.71199989318848</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1621198</v>
+        <v>1228634</v>
       </c>
       <c r="C2715" t="n">
-        <v>3.7279999256134</v>
+        <v>3.73600006103516</v>
       </c>
       <c r="D2715" t="n">
-        <v>3.70000004768372</v>
+        <v>3.69799995422363</v>
       </c>
       <c r="E2715" t="n">
-        <v>3.70000004768372</v>
+        <v>3.72199988365173</v>
       </c>
       <c r="F2715" t="n">
-        <v>3.71000003814697</v>
+        <v>3.71600008010864</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>2712538</v>
+        <v>1621198</v>
       </c>
       <c r="C2716" t="n">
-        <v>3.74799990653992</v>
+        <v>3.7279999256134</v>
       </c>
       <c r="D2716" t="n">
-        <v>3.61400008201599</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="E2716" t="n">
-        <v>3.69000005722046</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="F2716" t="n">
-        <v>3.62800002098083</v>
+        <v>3.71000003814697</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>2575827</v>
+        <v>2712538</v>
       </c>
       <c r="C2717" t="n">
-        <v>3.66599988937378</v>
+        <v>3.74799990653992</v>
       </c>
       <c r="D2717" t="n">
-        <v>3.60999989509583</v>
+        <v>3.61400008201599</v>
       </c>
       <c r="E2717" t="n">
-        <v>3.65599989891052</v>
+        <v>3.69000005722046</v>
       </c>
       <c r="F2717" t="n">
-        <v>3.60999989509583</v>
+        <v>3.62800002098083</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>2077532</v>
+        <v>2575827</v>
       </c>
       <c r="C2718" t="n">
-        <v>3.65400004386902</v>
+        <v>3.66599988937378</v>
       </c>
       <c r="D2718" t="n">
-        <v>3.62599992752075</v>
+        <v>3.60999989509583</v>
       </c>
       <c r="E2718" t="n">
-        <v>3.63599991798401</v>
+        <v>3.65599989891052</v>
       </c>
       <c r="F2718" t="n">
-        <v>3.63800001144409</v>
+        <v>3.60999989509583</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>1772729</v>
+        <v>2077532</v>
       </c>
       <c r="C2719" t="n">
-        <v>3.64599990844727</v>
+        <v>3.65400004386902</v>
       </c>
       <c r="D2719" t="n">
-        <v>3.56200003623962</v>
+        <v>3.62599992752075</v>
       </c>
       <c r="E2719" t="n">
-        <v>3.64000010490417</v>
+        <v>3.63599991798401</v>
       </c>
       <c r="F2719" t="n">
-        <v>3.56200003623962</v>
+        <v>3.63800001144409</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1952231</v>
+        <v>1772729</v>
       </c>
       <c r="C2720" t="n">
-        <v>3.58599996566772</v>
+        <v>3.64599990844727</v>
       </c>
       <c r="D2720" t="n">
-        <v>3.51200008392334</v>
+        <v>3.56200003623962</v>
       </c>
       <c r="E2720" t="n">
-        <v>3.55999994277954</v>
+        <v>3.64000010490417</v>
       </c>
       <c r="F2720" t="n">
-        <v>3.57800006866455</v>
+        <v>3.56200003623962</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>2390492</v>
+        <v>1952231</v>
       </c>
       <c r="C2721" t="n">
-        <v>3.64000010490417</v>
+        <v>3.58599996566772</v>
       </c>
       <c r="D2721" t="n">
-        <v>3.58400011062622</v>
+        <v>3.51200008392334</v>
       </c>
       <c r="E2721" t="n">
-        <v>3.59599995613098</v>
+        <v>3.55999994277954</v>
       </c>
       <c r="F2721" t="n">
-        <v>3.64000010490417</v>
+        <v>3.57800006866455</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>2715451</v>
+        <v>2390492</v>
       </c>
       <c r="C2722" t="n">
-        <v>3.71199989318848</v>
+        <v>3.64000010490417</v>
       </c>
       <c r="D2722" t="n">
+        <v>3.58400011062622</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.59599995613098</v>
+      </c>
+      <c r="F2722" t="n">
         <v>3.64000010490417</v>
       </c>
-      <c r="E2722" t="n">
-        <v>3.64000010490417</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>3.71199989318848</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>8934260</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>3.69400000572205</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>3.57200002670288</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>3.68799996376038</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G2" t="n">
-        <v>1.63574469089508</v>
+        <v>1.6357444524765</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G4" t="n">
-        <v>1.63440573215485</v>
+        <v>1.63440597057343</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63842141628265</v>
+        <v>1.63842153549194</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G6" t="n">
-        <v>1.61700427532196</v>
+        <v>1.61700451374054</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6531457901001</v>
+        <v>1.65314614772797</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71605920791626</v>
+        <v>1.71605944633484</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71873652935028</v>
+        <v>1.71873641014099</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69598078727722</v>
+        <v>1.69598042964935</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67322480678558</v>
+        <v>1.67322468757629</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63172876834869</v>
+        <v>1.63172900676727</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G13" t="n">
-        <v>1.69865798950195</v>
+        <v>1.69865787029266</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G15" t="n">
-        <v>1.69196510314941</v>
+        <v>1.69196498394012</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G16" t="n">
-        <v>1.72944509983063</v>
+        <v>1.72944521903992</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G17" t="n">
-        <v>1.71472060680389</v>
+        <v>1.71472084522247</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72810649871826</v>
+        <v>1.72810661792755</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75755524635315</v>
+        <v>1.75755512714386</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>1.72676777839661</v>
+        <v>1.72676825523376</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G23" t="n">
-        <v>1.77763402462006</v>
+        <v>1.77763378620148</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G24" t="n">
-        <v>1.76290965080261</v>
+        <v>1.76290953159332</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G25" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G26" t="n">
-        <v>1.75220108032227</v>
+        <v>1.75220084190369</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6558233499527</v>
+        <v>1.65582323074341</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G28" t="n">
-        <v>1.66787016391754</v>
+        <v>1.6678706407547</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62771284580231</v>
+        <v>1.62771308422089</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G32" t="n">
-        <v>1.72007501125336</v>
+        <v>1.72007489204407</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G33" t="n">
-        <v>1.70802795886993</v>
+        <v>1.70802772045135</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G34" t="n">
-        <v>1.71873652935028</v>
+        <v>1.71873641014099</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G35" t="n">
-        <v>1.71605920791626</v>
+        <v>1.71605944633484</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G38" t="n">
-        <v>1.7227520942688</v>
+        <v>1.72275221347809</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G39" t="n">
-        <v>1.72542917728424</v>
+        <v>1.72542929649353</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G40" t="n">
-        <v>1.74416959285736</v>
+        <v>1.74416935443878</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>1.75353956222534</v>
+        <v>1.75353980064392</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>1.7133823633194</v>
+        <v>1.71338200569153</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G45" t="n">
-        <v>1.67188620567322</v>
+        <v>1.67188632488251</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G46" t="n">
-        <v>1.66653192043304</v>
+        <v>1.66653180122375</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65716183185577</v>
+        <v>1.65716195106506</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G48" t="n">
-        <v>1.67054760456085</v>
+        <v>1.67054772377014</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G50" t="n">
-        <v>1.6892876625061</v>
+        <v>1.68928754329681</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G51" t="n">
-        <v>1.70401203632355</v>
+        <v>1.70401191711426</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.68661034107208</v>
+        <v>1.68661057949066</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G53" t="n">
-        <v>1.72007501125336</v>
+        <v>1.72007489204407</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>1.69999635219574</v>
+        <v>1.69999647140503</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>1.72141361236572</v>
+        <v>1.72141373157501</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G57" t="n">
-        <v>1.73479950428009</v>
+        <v>1.73479962348938</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.72141361236572</v>
+        <v>1.72141373157501</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G61" t="n">
-        <v>1.76558685302734</v>
+        <v>1.76558661460876</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>1.76558685302734</v>
+        <v>1.76558661460876</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75755524635315</v>
+        <v>1.75755512714386</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G64" t="n">
-        <v>1.75220108032227</v>
+        <v>1.75220084190369</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G65" t="n">
-        <v>1.75755524635315</v>
+        <v>1.75755512714386</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G66" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>1.69999635219574</v>
+        <v>1.69999647140503</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G71" t="n">
-        <v>1.69865798950195</v>
+        <v>1.69865787029266</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.69865798950195</v>
+        <v>1.69865787029266</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71204352378845</v>
+        <v>1.71204376220703</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G77" t="n">
-        <v>1.70267343521118</v>
+        <v>1.7026731967926</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.5</v>
       </c>
       <c r="G78" t="n">
-        <v>1.67322480678558</v>
+        <v>1.67322468757629</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.5</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67322480678558</v>
+        <v>1.67322468757629</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G81" t="n">
-        <v>1.70535063743591</v>
+        <v>1.70535087585449</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G82" t="n">
-        <v>1.73212242126465</v>
+        <v>1.73212206363678</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>1.72676777839661</v>
+        <v>1.72676825523376</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G84" t="n">
-        <v>1.75755524635315</v>
+        <v>1.75755512714386</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71605920791626</v>
+        <v>1.71605944633484</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>1.73346078395844</v>
+        <v>1.73346066474915</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G88" t="n">
-        <v>1.73212242126465</v>
+        <v>1.73212206363678</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G89" t="n">
-        <v>1.73346078395844</v>
+        <v>1.73346066474915</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G91" t="n">
-        <v>1.74416959285736</v>
+        <v>1.74416935443878</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G92" t="n">
-        <v>1.71204352378845</v>
+        <v>1.71204376220703</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G93" t="n">
-        <v>1.71739792823792</v>
+        <v>1.71739780902863</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G94" t="n">
-        <v>1.72007501125336</v>
+        <v>1.72007489204407</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>1.73346078395844</v>
+        <v>1.73346066474915</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G96" t="n">
-        <v>1.70936644077301</v>
+        <v>1.70936620235443</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.7133823633194</v>
+        <v>1.71338200569153</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G98" t="n">
-        <v>1.68259489536285</v>
+        <v>1.68259465694427</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67456340789795</v>
+        <v>1.67456305027008</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>1.70802795886993</v>
+        <v>1.70802772045135</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72542917728424</v>
+        <v>1.72542929649353</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G102" t="n">
-        <v>1.73346078395844</v>
+        <v>1.73346066474915</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G103" t="n">
-        <v>1.74952399730682</v>
+        <v>1.74952375888824</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75353956222534</v>
+        <v>1.75353980064392</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76826393604279</v>
+        <v>1.7682638168335</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G107" t="n">
-        <v>1.75487804412842</v>
+        <v>1.75487840175629</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75621664524078</v>
+        <v>1.75621676445007</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G112" t="n">
-        <v>1.74818527698517</v>
+        <v>1.74818539619446</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G113" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G114" t="n">
-        <v>1.73747658729553</v>
+        <v>1.73747634887695</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G115" t="n">
-        <v>1.68794941902161</v>
+        <v>1.68794918060303</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G116" t="n">
-        <v>1.65850043296814</v>
+        <v>1.65850019454956</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6692088842392</v>
+        <v>1.66920924186707</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>1.63976049423218</v>
+        <v>1.63976037502289</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G120" t="n">
-        <v>1.68358778953552</v>
+        <v>1.6835880279541</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G121" t="n">
-        <v>1.69885492324829</v>
+        <v>1.69885516166687</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G122" t="n">
-        <v>1.66693234443665</v>
+        <v>1.66693246364594</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G123" t="n">
-        <v>1.68497598171234</v>
+        <v>1.68497574329376</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G124" t="n">
-        <v>1.63223338127136</v>
+        <v>1.63223361968994</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G125" t="n">
-        <v>1.60308659076691</v>
+        <v>1.60308635234833</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>1.6655445098877</v>
+        <v>1.66554439067841</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G128" t="n">
-        <v>1.70579504966736</v>
+        <v>1.70579516887665</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G129" t="n">
-        <v>1.75714933872223</v>
+        <v>1.75714921951294</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G130" t="n">
-        <v>1.73216617107391</v>
+        <v>1.7321662902832</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G134" t="n">
-        <v>1.65444099903107</v>
+        <v>1.65444076061249</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>1.68636357784271</v>
+        <v>1.686363697052</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>1.67248392105103</v>
+        <v>1.67248427867889</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>1.6655445098877</v>
+        <v>1.66554439067841</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G138" t="n">
-        <v>1.69607937335968</v>
+        <v>1.69607949256897</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G140" t="n">
-        <v>1.68775129318237</v>
+        <v>1.68775153160095</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G141" t="n">
-        <v>1.69469118118286</v>
+        <v>1.69469141960144</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>1.70024347305298</v>
+        <v>1.70024359226227</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.70024347305298</v>
+        <v>1.70024359226227</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G145" t="n">
-        <v>1.69885492324829</v>
+        <v>1.69885516166687</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G146" t="n">
-        <v>1.68775129318237</v>
+        <v>1.68775153160095</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G147" t="n">
-        <v>1.70857095718384</v>
+        <v>1.70857083797455</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G151" t="n">
-        <v>1.77241694927216</v>
+        <v>1.772416472435</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G152" t="n">
-        <v>1.75853741168976</v>
+        <v>1.75853717327118</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G153" t="n">
-        <v>1.77241694927216</v>
+        <v>1.772416472435</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G154" t="n">
-        <v>1.78768420219421</v>
+        <v>1.7876843214035</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75437366962433</v>
+        <v>1.75437378883362</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G156" t="n">
-        <v>1.76686489582062</v>
+        <v>1.76686477661133</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.721062541008</v>
+        <v>1.72106277942657</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G158" t="n">
-        <v>1.74326980113983</v>
+        <v>1.74326992034912</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G159" t="n">
-        <v>1.73633003234863</v>
+        <v>1.73632979393005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G160" t="n">
-        <v>1.73216617107391</v>
+        <v>1.7321662902832</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G161" t="n">
-        <v>1.69469118118286</v>
+        <v>1.69469141960144</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G162" t="n">
-        <v>1.70024347305298</v>
+        <v>1.70024359226227</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69885492324829</v>
+        <v>1.69885516166687</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>1.67109608650208</v>
+        <v>1.67109632492065</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>1.69330382347107</v>
+        <v>1.6933034658432</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G168" t="n">
-        <v>1.70163106918335</v>
+        <v>1.70163118839264</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.70024347305298</v>
+        <v>1.70024359226227</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G171" t="n">
-        <v>1.72383844852448</v>
+        <v>1.72383832931519</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.68636357784271</v>
+        <v>1.686363697052</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G173" t="n">
-        <v>1.71134698390961</v>
+        <v>1.71134686470032</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G175" t="n">
-        <v>1.71412265300751</v>
+        <v>1.71412289142609</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G177" t="n">
-        <v>1.75714933872223</v>
+        <v>1.75714921951294</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G178" t="n">
-        <v>1.68775129318237</v>
+        <v>1.68775153160095</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G180" t="n">
-        <v>1.66276836395264</v>
+        <v>1.66276824474335</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>1.67248392105103</v>
+        <v>1.67248427867889</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G182" t="n">
-        <v>1.66276836395264</v>
+        <v>1.66276824474335</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G183" t="n">
-        <v>1.63500928878784</v>
+        <v>1.63500964641571</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G184" t="n">
-        <v>1.66415643692017</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G186" t="n">
-        <v>1.66415643692017</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.63917326927185</v>
+        <v>1.63917350769043</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G189" t="n">
-        <v>1.63639724254608</v>
+        <v>1.63639748096466</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63084518909454</v>
+        <v>1.63084554672241</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G191" t="n">
-        <v>1.62112998962402</v>
+        <v>1.62112963199615</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>1.64472496509552</v>
+        <v>1.64472484588623</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G193" t="n">
-        <v>1.66415643692017</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G194" t="n">
-        <v>1.62529385089874</v>
+        <v>1.62529373168945</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G195" t="n">
-        <v>1.56283605098724</v>
+        <v>1.56283581256866</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G196" t="n">
-        <v>1.53785264492035</v>
+        <v>1.53785276412964</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G197" t="n">
-        <v>1.52536118030548</v>
+        <v>1.5253609418869</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G199" t="n">
-        <v>1.53368890285492</v>
+        <v>1.53368866443634</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G201" t="n">
-        <v>1.54618012905121</v>
+        <v>1.54618036746979</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G202" t="n">
-        <v>1.55312013626099</v>
+        <v>1.55312025547028</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G203" t="n">
-        <v>1.5642237663269</v>
+        <v>1.56422352790833</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G204" t="n">
-        <v>1.5503443479538</v>
+        <v>1.55034422874451</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G205" t="n">
-        <v>1.56977546215057</v>
+        <v>1.56977570056915</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G206" t="n">
-        <v>1.5683878660202</v>
+        <v>1.56838750839233</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G207" t="n">
-        <v>1.58087933063507</v>
+        <v>1.58087921142578</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G208" t="n">
-        <v>1.55450820922852</v>
+        <v>1.55450809001923</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>1.54756832122803</v>
+        <v>1.54756844043732</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G211" t="n">
-        <v>1.55728375911713</v>
+        <v>1.55728399753571</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>1.61696600914001</v>
+        <v>1.61696588993073</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.60308659076691</v>
+        <v>1.60308635234833</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55450820922852</v>
+        <v>1.55450809001923</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>1.49760210514069</v>
+        <v>1.49760186672211</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>1.47817075252533</v>
+        <v>1.47817087173462</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G222" t="n">
-        <v>1.39905738830566</v>
+        <v>1.39905726909637</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>1.40183317661285</v>
+        <v>1.40183305740356</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G225" t="n">
-        <v>1.38448369503021</v>
+        <v>1.3844838142395</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G226" t="n">
-        <v>1.38934171199799</v>
+        <v>1.38934183120728</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G227" t="n">
-        <v>1.36991035938263</v>
+        <v>1.36991024017334</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G228" t="n">
-        <v>1.36227643489838</v>
+        <v>1.36227655410767</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G231" t="n">
-        <v>1.3497850894928</v>
+        <v>1.34978485107422</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G232" t="n">
-        <v>1.35325467586517</v>
+        <v>1.35325479507446</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G233" t="n">
-        <v>1.33937513828278</v>
+        <v>1.33937537670135</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>1.34284508228302</v>
+        <v>1.34284520149231</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G235" t="n">
-        <v>1.34631526470184</v>
+        <v>1.34631502628326</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G237" t="n">
-        <v>1.32341372966766</v>
+        <v>1.32341384887695</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G238" t="n">
-        <v>1.3019003868103</v>
+        <v>1.30190062522888</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G239" t="n">
-        <v>1.31924986839294</v>
+        <v>1.31924998760223</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40183317661285</v>
+        <v>1.40183305740356</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G242" t="n">
-        <v>1.41848826408386</v>
+        <v>1.41848862171173</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G244" t="n">
-        <v>1.42265248298645</v>
+        <v>1.42265260219574</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G245" t="n">
-        <v>1.46845495700836</v>
+        <v>1.46845507621765</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>1.44347167015076</v>
+        <v>1.44347178936005</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G249" t="n">
-        <v>1.48372232913971</v>
+        <v>1.48372256755829</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>1.49205040931702</v>
+        <v>1.49205029010773</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G251" t="n">
-        <v>1.50454151630402</v>
+        <v>1.50454163551331</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G252" t="n">
-        <v>1.50454151630402</v>
+        <v>1.50454163551331</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G253" t="n">
-        <v>1.50454151630402</v>
+        <v>1.50454163551331</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G254" t="n">
-        <v>1.52397310733795</v>
+        <v>1.52397298812866</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G255" t="n">
-        <v>1.50315392017365</v>
+        <v>1.50315368175507</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G257" t="n">
-        <v>1.52119719982147</v>
+        <v>1.52119731903076</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G258" t="n">
-        <v>1.54062855243683</v>
+        <v>1.54062879085541</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53785264492035</v>
+        <v>1.53785276412964</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G260" t="n">
-        <v>1.52952492237091</v>
+        <v>1.52952480316162</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G261" t="n">
-        <v>1.53230059146881</v>
+        <v>1.53230082988739</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G262" t="n">
-        <v>1.52119719982147</v>
+        <v>1.52119731903076</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G263" t="n">
-        <v>1.49898993968964</v>
+        <v>1.49899005889893</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>1.58226704597473</v>
+        <v>1.58226728439331</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>1.58226704597473</v>
+        <v>1.58226728439331</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57255148887634</v>
+        <v>1.57255160808563</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G270" t="n">
-        <v>1.58365535736084</v>
+        <v>1.58365511894226</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G275" t="n">
-        <v>1.5683878660202</v>
+        <v>1.56838750839233</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G276" t="n">
-        <v>1.573939204216</v>
+        <v>1.57393944263458</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G277" t="n">
-        <v>1.55728375911713</v>
+        <v>1.55728399753571</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G278" t="n">
-        <v>1.5087057352066</v>
+        <v>1.50870585441589</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G279" t="n">
-        <v>1.49760210514069</v>
+        <v>1.49760186672211</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G281" t="n">
-        <v>1.51148152351379</v>
+        <v>1.5114814043045</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G283" t="n">
-        <v>1.48649847507477</v>
+        <v>1.48649835586548</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>1.54062855243683</v>
+        <v>1.54062879085541</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>1.5683878660202</v>
+        <v>1.56838750839233</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.58226704597473</v>
+        <v>1.58226728439331</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G290" t="n">
-        <v>1.58087933063507</v>
+        <v>1.58087921142578</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G291" t="n">
-        <v>1.61141419410706</v>
+        <v>1.61141443252563</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="n">
-        <v>1.59614658355713</v>
+        <v>1.59614670276642</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G293" t="n">
-        <v>1.60725033283234</v>
+        <v>1.60725045204163</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>1.63084518909454</v>
+        <v>1.63084554672241</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G295" t="n">
-        <v>1.63639724254608</v>
+        <v>1.63639748096466</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G297" t="n">
-        <v>1.62251770496368</v>
+        <v>1.62251782417297</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.62668180465698</v>
+        <v>1.62668192386627</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G301" t="n">
-        <v>1.64194929599762</v>
+        <v>1.64194917678833</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>1.64472496509552</v>
+        <v>1.64472484588623</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G304" t="n">
-        <v>1.6613804101944</v>
+        <v>1.66138064861298</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G307" t="n">
-        <v>1.64333736896515</v>
+        <v>1.64333724975586</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.64611303806305</v>
+        <v>1.64611291885376</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G309" t="n">
-        <v>1.6683201789856</v>
+        <v>1.66832029819489</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G310" t="n">
-        <v>1.66415643692017</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>1.7071830034256</v>
+        <v>1.70718264579773</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G312" t="n">
-        <v>1.71273481845856</v>
+        <v>1.71273469924927</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G313" t="n">
-        <v>1.73771786689758</v>
+        <v>1.73771798610687</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75298535823822</v>
+        <v>1.75298523902893</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>1.79046010971069</v>
+        <v>1.79046046733856</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>1.79046010971069</v>
+        <v>1.79046046733856</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G317" t="n">
-        <v>1.81960701942444</v>
+        <v>1.8196074962616</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G318" t="n">
-        <v>1.83348679542542</v>
+        <v>1.8334869146347</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G319" t="n">
-        <v>1.83487474918365</v>
+        <v>1.83487451076508</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G320" t="n">
-        <v>1.80156397819519</v>
+        <v>1.80156373977661</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G321" t="n">
-        <v>1.79323601722717</v>
+        <v>1.79323637485504</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G322" t="n">
-        <v>1.80989170074463</v>
+        <v>1.80989158153534</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G324" t="n">
-        <v>1.82515919208527</v>
+        <v>1.82515907287598</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G325" t="n">
-        <v>1.83487474918365</v>
+        <v>1.83487451076508</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.83487474918365</v>
+        <v>1.83487451076508</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G327" t="n">
-        <v>1.83487474918365</v>
+        <v>1.83487451076508</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G328" t="n">
-        <v>1.83209884166718</v>
+        <v>1.83209908008575</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G329" t="n">
-        <v>1.86263370513916</v>
+        <v>1.86263346672058</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G330" t="n">
-        <v>1.85569417476654</v>
+        <v>1.85569405555725</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G331" t="n">
-        <v>1.83209884166718</v>
+        <v>1.83209908008575</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G332" t="n">
-        <v>1.83487474918365</v>
+        <v>1.83487451076508</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G334" t="n">
-        <v>1.79046010971069</v>
+        <v>1.79046046733856</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G336" t="n">
-        <v>1.84736597537994</v>
+        <v>1.84736633300781</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>1.81821918487549</v>
+        <v>1.8182190656662</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.80850374698639</v>
+        <v>1.8085036277771</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G340" t="n">
-        <v>1.82238304615021</v>
+        <v>1.8223831653595</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G341" t="n">
-        <v>1.83626270294189</v>
+        <v>1.8362625837326</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G343" t="n">
-        <v>1.85430610179901</v>
+        <v>1.85430634021759</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G344" t="n">
-        <v>1.85708212852478</v>
+        <v>1.8570818901062</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G345" t="n">
-        <v>1.86679744720459</v>
+        <v>1.86679756641388</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G346" t="n">
-        <v>1.91121196746826</v>
+        <v>1.91121220588684</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G347" t="n">
-        <v>1.94313526153564</v>
+        <v>1.94313514232635</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G348" t="n">
-        <v>1.97089385986328</v>
+        <v>1.97089421749115</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G349" t="n">
-        <v>1.98199796676636</v>
+        <v>1.98199772834778</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G350" t="n">
-        <v>1.96534240245819</v>
+        <v>1.9653422832489</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>1.97783410549164</v>
+        <v>1.97783362865448</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>1.9861615896225</v>
+        <v>1.98616182804108</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G355" t="n">
-        <v>1.99865305423737</v>
+        <v>1.99865329265594</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>2.02224826812744</v>
+        <v>2.0222487449646</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>2.01253271102905</v>
+        <v>2.01253318786621</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>1.96811830997467</v>
+        <v>1.96811854839325</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G361" t="n">
-        <v>2.00142908096313</v>
+        <v>2.00142931938171</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G362" t="n">
-        <v>2.03335237503052</v>
+        <v>2.03335189819336</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="n">
-        <v>1.99865305423737</v>
+        <v>1.99865329265594</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G365" t="n">
-        <v>1.9861615896225</v>
+        <v>1.98616182804108</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G366" t="n">
-        <v>2.01530885696411</v>
+        <v>2.01530861854553</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>2.01253271102905</v>
+        <v>2.01253318786621</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G369" t="n">
-        <v>2.01947259902954</v>
+        <v>2.01947236061096</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>2.0569474697113</v>
+        <v>2.05694723129272</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G371" t="n">
-        <v>2.04306793212891</v>
+        <v>2.04306721687317</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>2.06388735771179</v>
+        <v>2.06388711929321</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G373" t="n">
-        <v>2.05278372764587</v>
+        <v>2.05278348922729</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G374" t="n">
-        <v>2.06527495384216</v>
+        <v>2.06527543067932</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G376" t="n">
-        <v>2.08674359321594</v>
+        <v>2.08674335479736</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G378" t="n">
-        <v>2.06527495384216</v>
+        <v>2.06527543067932</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G379" t="n">
-        <v>2.01088809967041</v>
+        <v>2.01088786125183</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G381" t="n">
-        <v>1.98512601852417</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G382" t="n">
-        <v>1.97224462032318</v>
+        <v>1.97224497795105</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>1.93216979503632</v>
+        <v>1.9321700334549</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G385" t="n">
-        <v>1.92644476890564</v>
+        <v>1.92644512653351</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G386" t="n">
-        <v>1.92358231544495</v>
+        <v>1.92358243465424</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G387" t="n">
-        <v>1.91356384754181</v>
+        <v>1.91356408596039</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G388" t="n">
-        <v>1.86919581890106</v>
+        <v>1.86919558048248</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G389" t="n">
-        <v>1.88780176639557</v>
+        <v>1.88780152797699</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G391" t="n">
-        <v>1.89925158023834</v>
+        <v>1.89925169944763</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94505095481873</v>
+        <v>1.9450511932373</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96651947498322</v>
+        <v>1.9665195941925</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G395" t="n">
-        <v>1.9536384344101</v>
+        <v>1.95363855361938</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G397" t="n">
-        <v>1.95936357975006</v>
+        <v>1.95936322212219</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>1.93932628631592</v>
+        <v>1.9393265247345</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>1.98941957950592</v>
+        <v>1.98941934108734</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G401" t="n">
-        <v>1.98512601852417</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G402" t="n">
-        <v>1.98941957950592</v>
+        <v>1.98941934108734</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G403" t="n">
-        <v>1.94791376590729</v>
+        <v>1.94791328907013</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G404" t="n">
-        <v>1.9293075799942</v>
+        <v>1.92930781841278</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>1.9536384344101</v>
+        <v>1.95363855361938</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G407" t="n">
-        <v>1.957932472229</v>
+        <v>1.95793223381042</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G408" t="n">
-        <v>1.9565007686615</v>
+        <v>1.95650124549866</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G410" t="n">
-        <v>1.96222615242004</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G411" t="n">
-        <v>1.96365714073181</v>
+        <v>1.96365737915039</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>1.9536384344101</v>
+        <v>1.95363855361938</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G413" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G414" t="n">
-        <v>1.91785752773285</v>
+        <v>1.91785776615143</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G415" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G417" t="n">
-        <v>1.96651947498322</v>
+        <v>1.9665195941925</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>1.93932628631592</v>
+        <v>1.9393265247345</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>1.94934475421906</v>
+        <v>1.94934463500977</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G422" t="n">
-        <v>1.92358231544495</v>
+        <v>1.92358243465424</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G424" t="n">
-        <v>1.8920955657959</v>
+        <v>1.89209544658661</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G425" t="n">
-        <v>1.87921416759491</v>
+        <v>1.87921440601349</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G426" t="n">
-        <v>1.88493943214417</v>
+        <v>1.8849390745163</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G427" t="n">
-        <v>1.92358231544495</v>
+        <v>1.92358243465424</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>1.94075703620911</v>
+        <v>1.94075763225555</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G429" t="n">
-        <v>1.92787635326385</v>
+        <v>1.92787611484528</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G430" t="n">
-        <v>1.92501401901245</v>
+        <v>1.92501366138458</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G431" t="n">
-        <v>1.91928887367249</v>
+        <v>1.9192887544632</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G432" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G433" t="n">
-        <v>1.957932472229</v>
+        <v>1.95793223381042</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G434" t="n">
-        <v>1.99085092544556</v>
+        <v>1.99085080623627</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G435" t="n">
-        <v>1.96222615242004</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G437" t="n">
-        <v>1.93216979503632</v>
+        <v>1.9321700334549</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.91928887367249</v>
+        <v>1.9192887544632</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G439" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G441" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360126018524</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G442" t="n">
-        <v>1.92358231544495</v>
+        <v>1.92358243465424</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G443" t="n">
-        <v>1.91642653942108</v>
+        <v>1.9164263010025</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G444" t="n">
-        <v>1.92787635326385</v>
+        <v>1.92787611484528</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G445" t="n">
-        <v>1.94791376590729</v>
+        <v>1.94791328907013</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G446" t="n">
-        <v>1.92787635326385</v>
+        <v>1.92787611484528</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>1.90211403369904</v>
+        <v>1.9021143913269</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G448" t="n">
-        <v>1.90354549884796</v>
+        <v>1.90354537963867</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G449" t="n">
-        <v>1.91785752773285</v>
+        <v>1.91785776615143</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>1.91785752773285</v>
+        <v>1.91785776615143</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G451" t="n">
-        <v>1.88923287391663</v>
+        <v>1.88923311233521</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G452" t="n">
-        <v>1.92787635326385</v>
+        <v>1.92787611484528</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>1.88923287391663</v>
+        <v>1.88923311233521</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G454" t="n">
-        <v>1.93646371364594</v>
+        <v>1.93646395206451</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>1.93932628631592</v>
+        <v>1.9393265247345</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G460" t="n">
-        <v>1.957932472229</v>
+        <v>1.95793223381042</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G461" t="n">
-        <v>1.97224462032318</v>
+        <v>1.97224497795105</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G463" t="n">
-        <v>1.98655700683594</v>
+        <v>1.98655712604523</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G465" t="n">
-        <v>1.9765385389328</v>
+        <v>1.97653841972351</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="n">
-        <v>1.98512601852417</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G468" t="n">
-        <v>1.98798859119415</v>
+        <v>1.98798835277557</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G469" t="n">
-        <v>1.98941957950592</v>
+        <v>1.98941934108734</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G470" t="n">
-        <v>1.9765385389328</v>
+        <v>1.97653841972351</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G471" t="n">
-        <v>1.98798859119415</v>
+        <v>1.98798835277557</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G472" t="n">
-        <v>1.99657583236694</v>
+        <v>1.99657595157623</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G474" t="n">
-        <v>2.03521919250488</v>
+        <v>2.03521943092346</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G476" t="n">
-        <v>2.0695686340332</v>
+        <v>2.06956887245178</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G477" t="n">
-        <v>2.08960652351379</v>
+        <v>2.08960604667664</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.07529354095459</v>
+        <v>2.07529401779175</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G485" t="n">
-        <v>2.0996253490448</v>
+        <v>2.09962463378906</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G488" t="n">
-        <v>2.10105633735657</v>
+        <v>2.10105586051941</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G489" t="n">
-        <v>2.10248732566833</v>
+        <v>2.10248708724976</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G490" t="n">
-        <v>2.13111186027527</v>
+        <v>2.13111209869385</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>2.17548036575317</v>
+        <v>2.17548012733459</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G493" t="n">
-        <v>2.16403079032898</v>
+        <v>2.16403007507324</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G494" t="n">
-        <v>2.18549871444702</v>
+        <v>2.1854989528656</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G495" t="n">
-        <v>2.1983802318573</v>
+        <v>2.19837999343872</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G496" t="n">
-        <v>2.20839858055115</v>
+        <v>2.20839881896973</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G498" t="n">
-        <v>2.24131751060486</v>
+        <v>2.24131727218628</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G499" t="n">
-        <v>2.20839858055115</v>
+        <v>2.20839881896973</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G503" t="n">
-        <v>2.2069673538208</v>
+        <v>2.20696759223938</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G505" t="n">
-        <v>2.15973687171936</v>
+        <v>2.15973663330078</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.18263673782349</v>
+        <v>2.18263649940491</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G508" t="n">
-        <v>2.13540554046631</v>
+        <v>2.13540577888489</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G509" t="n">
-        <v>2.13254332542419</v>
+        <v>2.13254308700562</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.12538695335388</v>
+        <v>2.12538719177246</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G511" t="n">
-        <v>2.08245038986206</v>
+        <v>2.0824499130249</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G512" t="n">
-        <v>2.10248732566833</v>
+        <v>2.10248708724976</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G513" t="n">
-        <v>2.06384420394897</v>
+        <v>2.0638439655304</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>2.11823081970215</v>
+        <v>2.11823105812073</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G515" t="n">
-        <v>2.16546177864075</v>
+        <v>2.16546154022217</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G517" t="n">
-        <v>2.21412348747253</v>
+        <v>2.21412372589111</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3</v>
       </c>
       <c r="G518" t="n">
-        <v>2.14685535430908</v>
+        <v>2.14685559272766</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G519" t="n">
-        <v>2.17404913902283</v>
+        <v>2.17404890060425</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3</v>
       </c>
       <c r="G520" t="n">
-        <v>2.14685535430908</v>
+        <v>2.14685559272766</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.99600005149841</v>
       </c>
       <c r="G521" t="n">
-        <v>2.14399290084839</v>
+        <v>2.14399313926697</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G522" t="n">
-        <v>2.13540554046631</v>
+        <v>2.13540577888489</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G523" t="n">
-        <v>2.17404913902283</v>
+        <v>2.17404890060425</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G524" t="n">
-        <v>2.18120527267456</v>
+        <v>2.18120551109314</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G526" t="n">
-        <v>2.20267415046692</v>
+        <v>2.20267391204834</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G527" t="n">
-        <v>2.1983802318573</v>
+        <v>2.19837999343872</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G528" t="n">
-        <v>2.18120527267456</v>
+        <v>2.18120551109314</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G529" t="n">
-        <v>2.15258049964905</v>
+        <v>2.15258026123047</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G530" t="n">
-        <v>2.18406796455383</v>
+        <v>2.18406772613525</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G531" t="n">
-        <v>2.1511492729187</v>
+        <v>2.15114974975586</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G532" t="n">
-        <v>2.10248732566833</v>
+        <v>2.10248708724976</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G534" t="n">
-        <v>2.12538695335388</v>
+        <v>2.12538719177246</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G535" t="n">
-        <v>2.09246826171875</v>
+        <v>2.09246873855591</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G536" t="n">
-        <v>2.08245038986206</v>
+        <v>2.0824499130249</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G537" t="n">
-        <v>2.04523777961731</v>
+        <v>2.04523801803589</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G538" t="n">
-        <v>2.08245038986206</v>
+        <v>2.0824499130249</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G540" t="n">
-        <v>1.98655700683594</v>
+        <v>1.98655712604523</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G541" t="n">
-        <v>1.98798859119415</v>
+        <v>1.98798835277557</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G542" t="n">
-        <v>1.92787635326385</v>
+        <v>1.92787611484528</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G543" t="n">
-        <v>1.97081363201141</v>
+        <v>1.97081327438354</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G544" t="n">
-        <v>1.94361984729767</v>
+        <v>1.94361996650696</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G545" t="n">
-        <v>1.9765385389328</v>
+        <v>1.97653841972351</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G546" t="n">
-        <v>1.97224462032318</v>
+        <v>1.97224497795105</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>1.9293075799942</v>
+        <v>1.92930781841278</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G550" t="n">
-        <v>2.00659441947937</v>
+        <v>2.00659418106079</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G553" t="n">
-        <v>2.00516319274902</v>
+        <v>2.00516295433044</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G554" t="n">
-        <v>1.98798859119415</v>
+        <v>1.98798835277557</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G556" t="n">
-        <v>1.96222615242004</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>1.98226344585419</v>
+        <v>1.9822633266449</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G558" t="n">
-        <v>1.96222615242004</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G559" t="n">
-        <v>1.98512601852417</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G561" t="n">
-        <v>1.95506989955902</v>
+        <v>1.95506978034973</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G562" t="n">
-        <v>1.99800705909729</v>
+        <v>1.99800670146942</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G563" t="n">
-        <v>1.99514448642731</v>
+        <v>1.99514472484589</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>1.99371373653412</v>
+        <v>1.99371302127838</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G565" t="n">
-        <v>1.99514448642731</v>
+        <v>1.99514472484589</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G566" t="n">
-        <v>1.98798859119415</v>
+        <v>1.98798835277557</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>1.98226344585419</v>
+        <v>1.9822633266449</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G569" t="n">
-        <v>2.00945711135864</v>
+        <v>2.00945663452148</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G570" t="n">
-        <v>2.04523777961731</v>
+        <v>2.04523801803589</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>1.99657583236694</v>
+        <v>1.99657595157623</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G572" t="n">
-        <v>2.03092551231384</v>
+        <v>2.03092527389526</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G574" t="n">
-        <v>2.12824964523315</v>
+        <v>2.12824940681458</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>2.13683700561523</v>
+        <v>2.13683676719666</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G576" t="n">
-        <v>2.14828705787659</v>
+        <v>2.14828681945801</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.13540554046631</v>
+        <v>2.13540577888489</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G578" t="n">
-        <v>2.15973687171936</v>
+        <v>2.15973663330078</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G579" t="n">
-        <v>2.16832399368286</v>
+        <v>2.16832423210144</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G580" t="n">
-        <v>2.17404913902283</v>
+        <v>2.17404890060425</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G582" t="n">
-        <v>2.14113116264343</v>
+        <v>2.14113068580627</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G583" t="n">
-        <v>2.14113116264343</v>
+        <v>2.14113068580627</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3</v>
       </c>
       <c r="G584" t="n">
-        <v>2.14685535430908</v>
+        <v>2.14685559272766</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G587" t="n">
-        <v>2.16403079032898</v>
+        <v>2.16403007507324</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3</v>
       </c>
       <c r="G588" t="n">
-        <v>2.14685535430908</v>
+        <v>2.14685559272766</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G589" t="n">
-        <v>2.15830540657043</v>
+        <v>2.15830564498901</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>2.17548036575317</v>
+        <v>2.17548012733459</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G594" t="n">
-        <v>2.1983802318573</v>
+        <v>2.19837999343872</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G597" t="n">
-        <v>2.1983802318573</v>
+        <v>2.19837999343872</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G600" t="n">
-        <v>2.18263673782349</v>
+        <v>2.18263649940491</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G601" t="n">
-        <v>2.13397455215454</v>
+        <v>2.13397479057312</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G602" t="n">
-        <v>2.13111186027527</v>
+        <v>2.13111209869385</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G603" t="n">
-        <v>2.15687417984009</v>
+        <v>2.15687441825867</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G604" t="n">
-        <v>2.13111186027527</v>
+        <v>2.13111209869385</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G605" t="n">
-        <v>2.03092551231384</v>
+        <v>2.03092527389526</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G606" t="n">
-        <v>2.03521919250488</v>
+        <v>2.03521943092346</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>1.99657583236694</v>
+        <v>1.99657595157623</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.99657583236694</v>
+        <v>1.99657595157623</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G609" t="n">
-        <v>2.0509626865387</v>
+        <v>2.05096244812012</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G610" t="n">
-        <v>2.03092551231384</v>
+        <v>2.03092527389526</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.03235650062561</v>
+        <v>2.03235673904419</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G613" t="n">
-        <v>1.9378947019577</v>
+        <v>1.93789494037628</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86490213871002</v>
+        <v>1.86490190029144</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G615" t="n">
-        <v>1.88207697868347</v>
+        <v>1.88207685947418</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G616" t="n">
-        <v>1.897820353508</v>
+        <v>1.89782011508942</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G617" t="n">
-        <v>1.88637030124664</v>
+        <v>1.88637042045593</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G618" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360126018524</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G619" t="n">
-        <v>1.94648218154907</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89495801925659</v>
+        <v>1.8949579000473</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86633324623108</v>
+        <v>1.8663330078125</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G623" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360126018524</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G624" t="n">
-        <v>1.93646371364594</v>
+        <v>1.93646395206451</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G625" t="n">
-        <v>1.9378947019577</v>
+        <v>1.93789494037628</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>1.9536384344101</v>
+        <v>1.95363855361938</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G627" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360126018524</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G628" t="n">
-        <v>1.94324338436127</v>
+        <v>1.94324290752411</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G630" t="n">
-        <v>1.98477804660797</v>
+        <v>1.98477828502655</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G631" t="n">
-        <v>1.95214343070984</v>
+        <v>1.95214319229126</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>1.94324338436127</v>
+        <v>1.94324290752411</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G634" t="n">
-        <v>1.98626172542572</v>
+        <v>1.98626148700714</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G635" t="n">
-        <v>1.97291135787964</v>
+        <v>1.97291111946106</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G636" t="n">
-        <v>2.00109553337097</v>
+        <v>2.00109577178955</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G646" t="n">
-        <v>2.05746459960938</v>
+        <v>2.0574643611908</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G647" t="n">
-        <v>2.04411387443542</v>
+        <v>2.044114112854</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G648" t="n">
-        <v>2.04411387443542</v>
+        <v>2.044114112854</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07674860954285</v>
+        <v>2.07674884796143</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G650" t="n">
-        <v>2.08119893074036</v>
+        <v>2.08119869232178</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G651" t="n">
-        <v>2.06191468238831</v>
+        <v>2.06191444396973</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>2.06191468238831</v>
+        <v>2.06191444396973</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G654" t="n">
-        <v>2.01592922210693</v>
+        <v>2.01592946052551</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>2.1138334274292</v>
+        <v>2.11383318901062</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G659" t="n">
-        <v>2.10344958305359</v>
+        <v>2.10344982147217</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>2.07674860954285</v>
+        <v>2.07674884796143</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G662" t="n">
-        <v>2.06191468238831</v>
+        <v>2.06191444396973</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>2.07674860954285</v>
+        <v>2.07674884796143</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G664" t="n">
-        <v>2.12421703338623</v>
+        <v>2.12421727180481</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G666" t="n">
-        <v>2.09158229827881</v>
+        <v>2.09158253669739</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G667" t="n">
-        <v>2.07229852676392</v>
+        <v>2.07229828834534</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G670" t="n">
-        <v>2.04263067245483</v>
+        <v>2.04263043403625</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G671" t="n">
-        <v>2.03669667243958</v>
+        <v>2.03669691085815</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>2.03076338768005</v>
+        <v>2.03076314926147</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G673" t="n">
-        <v>2.07526516914368</v>
+        <v>2.07526540756226</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>2.06636524200439</v>
+        <v>2.06636476516724</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G678" t="n">
-        <v>2.00851225852966</v>
+        <v>2.00851249694824</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G679" t="n">
-        <v>2.01147890090942</v>
+        <v>2.011479139328</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G680" t="n">
-        <v>2.00257873535156</v>
+        <v>2.00257897377014</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G682" t="n">
-        <v>2.01889634132385</v>
+        <v>2.01889610290527</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G686" t="n">
-        <v>2.06191468238831</v>
+        <v>2.06191444396973</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G687" t="n">
-        <v>2.09603261947632</v>
+        <v>2.09603238105774</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.1138334274292</v>
+        <v>2.11383318901062</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G689" t="n">
-        <v>2.10789942741394</v>
+        <v>2.1078999042511</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>2.08416557312012</v>
+        <v>2.08416533470154</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G696" t="n">
-        <v>2.04411387443542</v>
+        <v>2.044114112854</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.0322470664978</v>
+        <v>2.03224682807922</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G698" t="n">
-        <v>2.0322470664978</v>
+        <v>2.03224682807922</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G699" t="n">
-        <v>2.02779626846313</v>
+        <v>2.02779650688171</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01592922210693</v>
+        <v>2.01592946052551</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G702" t="n">
-        <v>1.98477804660797</v>
+        <v>1.98477828502655</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>1.9818115234375</v>
+        <v>1.98181176185608</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G707" t="n">
-        <v>1.87945759296417</v>
+        <v>1.87945735454559</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85572338104248</v>
+        <v>1.85572290420532</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G710" t="n">
-        <v>1.85572338104248</v>
+        <v>1.85572290420532</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G711" t="n">
-        <v>1.82308852672577</v>
+        <v>1.82308876514435</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.40599989891052</v>
       </c>
       <c r="G712" t="n">
-        <v>1.78452038764954</v>
+        <v>1.78452026844025</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G714" t="n">
-        <v>1.79342079162598</v>
+        <v>1.7934205532074</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G715" t="n">
-        <v>1.81418812274933</v>
+        <v>1.8141884803772</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G716" t="n">
-        <v>1.82160544395447</v>
+        <v>1.82160520553589</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79342079162598</v>
+        <v>1.7934205532074</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G719" t="n">
-        <v>1.7815535068512</v>
+        <v>1.78155362606049</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G720" t="n">
-        <v>1.84682297706604</v>
+        <v>1.84682273864746</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G722" t="n">
-        <v>1.81122124195099</v>
+        <v>1.81122136116028</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>1.80973815917969</v>
+        <v>1.8097380399704</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>1.82457184791565</v>
+        <v>1.82457160949707</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G731" t="n">
-        <v>1.8957747220993</v>
+        <v>1.89577484130859</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G732" t="n">
-        <v>1.886873960495</v>
+        <v>1.88687419891357</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G733" t="n">
-        <v>1.89429128170013</v>
+        <v>1.89429104328156</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G734" t="n">
-        <v>1.86017322540283</v>
+        <v>1.86017298698425</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G736" t="n">
-        <v>1.8438560962677</v>
+        <v>1.84385621547699</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.83940601348877</v>
+        <v>1.83940613269806</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G739" t="n">
-        <v>1.82308852672577</v>
+        <v>1.82308876514435</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G740" t="n">
-        <v>1.81270492076874</v>
+        <v>1.81270503997803</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G741" t="n">
-        <v>1.82308852672577</v>
+        <v>1.82308876514435</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G742" t="n">
-        <v>1.84682297706604</v>
+        <v>1.84682273864746</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G743" t="n">
-        <v>1.84682297706604</v>
+        <v>1.84682273864746</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G744" t="n">
-        <v>1.82902228832245</v>
+        <v>1.82902216911316</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.40599989891052</v>
       </c>
       <c r="G745" t="n">
-        <v>1.78452038764954</v>
+        <v>1.78452026844025</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G746" t="n">
-        <v>1.79935431480408</v>
+        <v>1.79935443401337</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G752" t="n">
-        <v>1.79045403003693</v>
+        <v>1.79045391082764</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G753" t="n">
-        <v>1.8661071062088</v>
+        <v>1.86610698699951</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G758" t="n">
-        <v>1.97884476184845</v>
+        <v>1.97884452342987</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.00999593734741</v>
+        <v>2.00999641418457</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>2.00257873535156</v>
+        <v>2.00257897377014</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>1.99516212940216</v>
+        <v>1.99516189098358</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>2.01592922210693</v>
+        <v>2.01592946052551</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G765" t="n">
-        <v>2.06191468238831</v>
+        <v>2.06191444396973</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G770" t="n">
-        <v>2.07674860954285</v>
+        <v>2.07674884796143</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G773" t="n">
-        <v>2.11680006980896</v>
+        <v>2.11680030822754</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G776" t="n">
-        <v>2.11086654663086</v>
+        <v>2.11086678504944</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G777" t="n">
-        <v>2.10789942741394</v>
+        <v>2.1078999042511</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G778" t="n">
-        <v>2.10641622543335</v>
+        <v>2.10641646385193</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G779" t="n">
-        <v>2.12421703338623</v>
+        <v>2.12421727180481</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G780" t="n">
-        <v>2.13311743736267</v>
+        <v>2.13311767578125</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G781" t="n">
-        <v>2.11680006980896</v>
+        <v>2.11680030822754</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G782" t="n">
-        <v>2.12421703338623</v>
+        <v>2.12421727180481</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G783" t="n">
-        <v>2.16575241088867</v>
+        <v>2.16575217247009</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G784" t="n">
-        <v>2.16723561286926</v>
+        <v>2.1672351360321</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>2.18800282478333</v>
+        <v>2.1880030632019</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G791" t="n">
-        <v>2.161301612854</v>
+        <v>2.16130208969116</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G794" t="n">
-        <v>2.20431971549988</v>
+        <v>2.20432019233704</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>2.21025395393372</v>
+        <v>2.21025371551514</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G797" t="n">
-        <v>2.19245314598083</v>
+        <v>2.19245338439941</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G801" t="n">
-        <v>2.22657132148743</v>
+        <v>2.22657108306885</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>2.1954197883606</v>
+        <v>2.19542002677917</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>2.16575241088867</v>
+        <v>2.16575217247009</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G805" t="n">
-        <v>2.17316913604736</v>
+        <v>2.17316889762878</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G808" t="n">
-        <v>2.20283675193787</v>
+        <v>2.20283699035645</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G815" t="n">
-        <v>2.16278529167175</v>
+        <v>2.16278505325317</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G816" t="n">
-        <v>2.14498448371887</v>
+        <v>2.14498472213745</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G817" t="n">
-        <v>2.24585556983948</v>
+        <v>2.2458553314209</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G818" t="n">
-        <v>2.27997350692749</v>
+        <v>2.27997326850891</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G820" t="n">
-        <v>2.30222415924072</v>
+        <v>2.3022243976593</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G824" t="n">
-        <v>2.3897442817688</v>
+        <v>2.38974404335022</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G825" t="n">
-        <v>2.38529419898987</v>
+        <v>2.38529396057129</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>2.40309476852417</v>
+        <v>2.40309453010559</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.25</v>
       </c>
       <c r="G831" t="n">
-        <v>2.41051173210144</v>
+        <v>2.41051149368286</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G836" t="n">
-        <v>2.35859322547913</v>
+        <v>2.35859298706055</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G838" t="n">
-        <v>2.36155962944031</v>
+        <v>2.36155986785889</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G842" t="n">
-        <v>2.34969258308411</v>
+        <v>2.34969234466553</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G843" t="n">
-        <v>2.36304354667664</v>
+        <v>2.36304330825806</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G844" t="n">
-        <v>2.36155962944031</v>
+        <v>2.36155986785889</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G845" t="n">
-        <v>2.34375929832458</v>
+        <v>2.34375905990601</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G847" t="n">
-        <v>2.36749362945557</v>
+        <v>2.36749339103699</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G849" t="n">
-        <v>2.32447528839111</v>
+        <v>2.32447504997253</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G850" t="n">
-        <v>2.3452422618866</v>
+        <v>2.34524250030518</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G851" t="n">
-        <v>2.32447528839111</v>
+        <v>2.32447504997253</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G852" t="n">
-        <v>2.32744169235229</v>
+        <v>2.32744193077087</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G854" t="n">
-        <v>2.38529419898987</v>
+        <v>2.38529396057129</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G855" t="n">
-        <v>2.42386198043823</v>
+        <v>2.42386221885681</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.30200004577637</v>
       </c>
       <c r="G859" t="n">
-        <v>2.44908022880554</v>
+        <v>2.44907999038696</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G860" t="n">
-        <v>2.45056319236755</v>
+        <v>2.45056343078613</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.25</v>
       </c>
       <c r="G862" t="n">
-        <v>2.41051173210144</v>
+        <v>2.41051149368286</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.30200004577637</v>
       </c>
       <c r="G863" t="n">
-        <v>2.44908022880554</v>
+        <v>2.44907999038696</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G864" t="n">
-        <v>2.42831206321716</v>
+        <v>2.42831230163574</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G865" t="n">
-        <v>2.42237877845764</v>
+        <v>2.42237901687622</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G867" t="n">
-        <v>2.3897442817688</v>
+        <v>2.38974404335022</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.25</v>
       </c>
       <c r="G868" t="n">
-        <v>2.41051173210144</v>
+        <v>2.41051149368286</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G872" t="n">
-        <v>2.48171424865723</v>
+        <v>2.48171448707581</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G873" t="n">
-        <v>2.49358153343201</v>
+        <v>2.49358177185059</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G875" t="n">
-        <v>2.49061512947083</v>
+        <v>2.49061489105225</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G876" t="n">
-        <v>2.49358153343201</v>
+        <v>2.49358177185059</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>2.49209809303284</v>
+        <v>2.49209856987</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G881" t="n">
-        <v>2.54105019569397</v>
+        <v>2.54105043411255</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G883" t="n">
-        <v>2.60186886787415</v>
+        <v>2.60186910629272</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G888" t="n">
-        <v>2.56827735900879</v>
+        <v>2.56827712059021</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G889" t="n">
-        <v>2.55453443527222</v>
+        <v>2.5545346736908</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G891" t="n">
-        <v>2.69348454475403</v>
+        <v>2.69348430633545</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G892" t="n">
-        <v>2.69043016433716</v>
+        <v>2.69043040275574</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>2.67974233627319</v>
+        <v>2.67974209785461</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G899" t="n">
-        <v>2.70875406265259</v>
+        <v>2.70875358581543</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G900" t="n">
-        <v>2.69348454475403</v>
+        <v>2.69348430633545</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G901" t="n">
-        <v>2.68890380859375</v>
+        <v>2.68890357017517</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G902" t="n">
-        <v>2.70875406265259</v>
+        <v>2.70875358581543</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G904" t="n">
-        <v>2.64309597015381</v>
+        <v>2.64309620857239</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G905" t="n">
-        <v>2.62935400009155</v>
+        <v>2.62935376167297</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>2.63393449783325</v>
+        <v>2.63393473625183</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G907" t="n">
-        <v>2.61713838577271</v>
+        <v>2.61713862419128</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G908" t="n">
-        <v>2.61408472061157</v>
+        <v>2.61408448219299</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G909" t="n">
-        <v>2.61866545677185</v>
+        <v>2.61866521835327</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G913" t="n">
-        <v>2.59728860855103</v>
+        <v>2.5972888469696</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G915" t="n">
-        <v>2.59270787239075</v>
+        <v>2.59270763397217</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>2.61866545677185</v>
+        <v>2.61866521835327</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G917" t="n">
-        <v>2.61255764961243</v>
+        <v>2.61255741119385</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G920" t="n">
-        <v>2.620192527771</v>
+        <v>2.62019228935242</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G923" t="n">
-        <v>2.67058038711548</v>
+        <v>2.67058062553406</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G924" t="n">
-        <v>2.6614191532135</v>
+        <v>2.66141939163208</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G925" t="n">
-        <v>2.66905379295349</v>
+        <v>2.66905403137207</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G927" t="n">
-        <v>2.67058038711548</v>
+        <v>2.67058062553406</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G933" t="n">
-        <v>2.76524925231934</v>
+        <v>2.76524972915649</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G935" t="n">
-        <v>2.79426097869873</v>
+        <v>2.79426121711731</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G938" t="n">
-        <v>2.69348454475403</v>
+        <v>2.69348430633545</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>2.68279576301575</v>
+        <v>2.68279600143433</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G940" t="n">
-        <v>2.67516136169434</v>
+        <v>2.67516112327576</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G941" t="n">
-        <v>2.72554969787598</v>
+        <v>2.7255494594574</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G942" t="n">
-        <v>2.69959187507629</v>
+        <v>2.69959211349487</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>2.70264577865601</v>
+        <v>2.70264601707458</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G945" t="n">
-        <v>2.78509950637817</v>
+        <v>2.78509926795959</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G946" t="n">
-        <v>2.76524925231934</v>
+        <v>2.76524972915649</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G947" t="n">
-        <v>2.78204560279846</v>
+        <v>2.78204584121704</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G949" t="n">
-        <v>2.82785296440125</v>
+        <v>2.82785320281982</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.89351034164429</v>
+        <v>2.89351081848145</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G957" t="n">
-        <v>2.88892960548401</v>
+        <v>2.88892936706543</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G958" t="n">
-        <v>2.89503765106201</v>
+        <v>2.89503788948059</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>2.89351034164429</v>
+        <v>2.89351081848145</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G962" t="n">
-        <v>2.87671446800232</v>
+        <v>2.8767147064209</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G963" t="n">
-        <v>2.88740301132202</v>
+        <v>2.8874032497406</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G964" t="n">
-        <v>2.89351034164429</v>
+        <v>2.89351081848145</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G969" t="n">
-        <v>2.88740301132202</v>
+        <v>2.8874032497406</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G978" t="n">
-        <v>2.94084525108337</v>
+        <v>2.94084501266479</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G980" t="n">
-        <v>2.92557621002197</v>
+        <v>2.92557597160339</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G981" t="n">
-        <v>2.88740301132202</v>
+        <v>2.8874032497406</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G984" t="n">
-        <v>2.94389915466309</v>
+        <v>2.94389891624451</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G985" t="n">
-        <v>2.94542622566223</v>
+        <v>2.94542598724365</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G986" t="n">
-        <v>2.96985697746277</v>
+        <v>2.96985673904419</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G989" t="n">
-        <v>3.05994510650635</v>
+        <v>3.05994486808777</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G990" t="n">
-        <v>3.08284854888916</v>
+        <v>3.08284878730774</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>3.06147170066833</v>
+        <v>3.06147193908691</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G996" t="n">
-        <v>3.04162168502808</v>
+        <v>3.0416214466095</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G999" t="n">
-        <v>2.95764112472534</v>
+        <v>2.95764136314392</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.97138333320618</v>
+        <v>2.97138357162476</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.94237208366394</v>
+        <v>2.94237232208252</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.98054480552673</v>
+        <v>2.98054504394531</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.96985697746277</v>
+        <v>2.96985673904419</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.03856801986694</v>
+        <v>3.03856778144836</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.03551435470581</v>
+        <v>3.03551459312439</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.03093314170837</v>
+        <v>3.03093338012695</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.03245997428894</v>
+        <v>3.03246021270752</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.97749137878418</v>
+        <v>2.9774911403656</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.98054480552673</v>
+        <v>2.98054504394531</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.94542622566223</v>
+        <v>2.94542598724365</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.94084525108337</v>
+        <v>2.94084501266479</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.94237208366394</v>
+        <v>2.94237232208252</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.9668025970459</v>
+        <v>2.96680283546448</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.97749137878418</v>
+        <v>2.9774911403656</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.96985697746277</v>
+        <v>2.96985673904419</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.01108336448669</v>
+        <v>3.01108312606812</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.04925656318665</v>
+        <v>3.04925632476807</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.23554039001465</v>
+        <v>3.23554062843323</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.17446327209473</v>
+        <v>3.17446351051331</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.30119824409485</v>
+        <v>3.30119776725769</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.13171005249023</v>
+        <v>3.13171029090881</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.13934469223022</v>
+        <v>3.13934445381165</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.14850640296936</v>
+        <v>3.14850616455078</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.23095965385437</v>
+        <v>3.23095989227295</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.2480001449585</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.24317502975464</v>
+        <v>3.24317526817322</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.29509043693542</v>
+        <v>3.29509019851685</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.30730557441711</v>
+        <v>3.30730533599854</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.38823246955872</v>
+        <v>3.38823270797729</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.19889426231384</v>
+        <v>3.19889450073242</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.14087152481079</v>
+        <v>3.14087128639221</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.96069526672363</v>
+        <v>2.96069502830505</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.04162168502808</v>
+        <v>3.0416214466095</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.13934469223022</v>
+        <v>3.13934445381165</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.9668025970459</v>
+        <v>2.96680283546448</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.71333432197571</v>
+        <v>2.71333408355713</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.57743883132935</v>
+        <v>2.57743859291077</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.12699770927429</v>
+        <v>2.12699747085571</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.4507040977478</v>
+        <v>2.45070433616638</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.36214280128479</v>
+        <v>2.36214303970337</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.41100430488586</v>
+        <v>2.41100406646729</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.35756230354309</v>
+        <v>2.35756254196167</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.4751353263855</v>
+        <v>2.47513508796692</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.36214280128479</v>
+        <v>2.36214303970337</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.33771228790283</v>
+        <v>2.33771252632141</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.39726209640503</v>
+        <v>2.39726233482361</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.4949848651886</v>
+        <v>2.49498510360718</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.4507040977478</v>
+        <v>2.45070433616638</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.44459676742554</v>
+        <v>2.44459652900696</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.45986557006836</v>
+        <v>2.45986580848694</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.43696236610413</v>
+        <v>2.43696212768555</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.51025438308716</v>
+        <v>2.51025414466858</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.25</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.48124289512634</v>
+        <v>2.48124241828918</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.56064248085022</v>
+        <v>2.5606427192688</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.41863918304443</v>
+        <v>2.41863894462585</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.41863918304443</v>
+        <v>2.41863894462585</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.48276972770691</v>
+        <v>2.48276948928833</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.37130451202393</v>
+        <v>2.3713047504425</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.19799995422363</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.44154262542725</v>
+        <v>2.44154286384583</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.61408472061157</v>
+        <v>2.61408448219299</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.63393449783325</v>
+        <v>2.63393473625183</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63393449783325</v>
+        <v>2.63393473625183</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.69348454475403</v>
+        <v>2.69348430633545</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.73623776435852</v>
+        <v>2.7362380027771</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.59728860855103</v>
+        <v>2.5972888469696</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.68432307243347</v>
+        <v>2.68432283401489</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.67210745811462</v>
+        <v>2.67210721969604</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.65378427505493</v>
+        <v>2.65378451347351</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.63851547241211</v>
+        <v>2.63851523399353</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.52705049514771</v>
+        <v>2.52705025672913</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.55453443527222</v>
+        <v>2.5545346736908</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.61866545677185</v>
+        <v>2.61866521835327</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.61103105545044</v>
+        <v>2.61103057861328</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.58586430549622</v>
+        <v>2.58586406707764</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.53081250190735</v>
+        <v>2.53081226348877</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.52294778823853</v>
+        <v>2.52294754981995</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.5622706413269</v>
+        <v>2.56227040290833</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.53867673873901</v>
+        <v>2.53867650032043</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.58114528656006</v>
+        <v>2.58114552497864</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.61574959754944</v>
+        <v>2.61574935913086</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.61889505386353</v>
+        <v>2.6188952922821</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.61103081703186</v>
+        <v>2.61103057861328</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.52294778823853</v>
+        <v>2.52294754981995</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.48362517356873</v>
+        <v>2.48362493515015</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.50092744827271</v>
+        <v>2.50092697143555</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.47890615463257</v>
+        <v>2.47890639305115</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.55597901344299</v>
+        <v>2.55597877502441</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.66922831535339</v>
+        <v>2.66922807693481</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.65979075431824</v>
+        <v>2.65979099273682</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.64248919487</v>
+        <v>2.64248871803284</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.61574959754944</v>
+        <v>2.61574935913086</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.5544056892395</v>
+        <v>2.55440592765808</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.55126023292542</v>
+        <v>2.55125999450684</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.25</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.55597901344299</v>
+        <v>2.55597877502441</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.51822876930237</v>
+        <v>2.51822900772095</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.5056459903717</v>
+        <v>2.50564575195312</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.57957243919373</v>
+        <v>2.5795726776123</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.53710412979126</v>
+        <v>2.53710389137268</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.52923941612244</v>
+        <v>2.52923965454102</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.55283331871033</v>
+        <v>2.55283308029175</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.59844756126404</v>
+        <v>2.59844732284546</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.52294778823853</v>
+        <v>2.52294754981995</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.52609372138977</v>
+        <v>2.52609348297119</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.51351046562195</v>
+        <v>2.51351022720337</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.53395795822144</v>
+        <v>2.53395819664001</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.51980209350586</v>
+        <v>2.51980185508728</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.47890615463257</v>
+        <v>2.47890639305115</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.44272923469543</v>
+        <v>2.44272947311401</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.48362517356873</v>
+        <v>2.48362493515015</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.45059370994568</v>
+        <v>2.45059394836426</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.40812540054321</v>
+        <v>2.40812516212463</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.39711499214172</v>
+        <v>2.3971152305603</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.28386545181274</v>
+        <v>2.28386521339417</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.27757382392883</v>
+        <v>2.27757358551025</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.10455369949341</v>
+        <v>2.10455393791199</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.12342834472656</v>
+        <v>2.12342858314514</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.1596052646637</v>
+        <v>2.15960550308228</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.21308445930481</v>
+        <v>2.21308422088623</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.3231885433197</v>
+        <v>2.32318806648254</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.34678173065186</v>
+        <v>2.34678196907043</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.4537398815155</v>
+        <v>2.45373964309692</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.39868831634521</v>
+        <v>2.39868807792664</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.41599035263062</v>
+        <v>2.41598987579346</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.42857336997986</v>
+        <v>2.42857313156128</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.3672297000885</v>
+        <v>2.36722993850708</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.31375074386597</v>
+        <v>2.31375050544739</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.2885844707489</v>
+        <v>2.28858423233032</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.26499032974243</v>
+        <v>2.26499056816101</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.34835505485535</v>
+        <v>2.34835481643677</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.2413969039917</v>
+        <v>2.24139666557312</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.28701138496399</v>
+        <v>2.28701114654541</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.3499276638031</v>
+        <v>2.34992742538452</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.34363627433777</v>
+        <v>2.34363603591919</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.38138604164124</v>
+        <v>2.38138580322266</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.48519825935364</v>
+        <v>2.48519802093506</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.42857336997986</v>
+        <v>2.42857313156128</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.43486499786377</v>
+        <v>2.43486475944519</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.39868831634521</v>
+        <v>2.39868807792664</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.23825120925903</v>
+        <v>2.23825097084045</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.87199997901917</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.2586989402771</v>
+        <v>2.25869870185852</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.26813673973083</v>
+        <v>2.26813650131226</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.26813673973083</v>
+        <v>2.26813650131226</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.2885844707489</v>
+        <v>2.28858423233032</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.44587540626526</v>
+        <v>2.44587516784668</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.4537398815155</v>
+        <v>2.45373964309692</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.48047924041748</v>
+        <v>2.4804790019989</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.43958353996277</v>
+        <v>2.43958330154419</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.41913557052612</v>
+        <v>2.41913533210754</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.3672297000885</v>
+        <v>2.36722993850708</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.34678173065186</v>
+        <v>2.34678196907043</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.3231885433197</v>
+        <v>2.32318806648254</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.2885844707489</v>
+        <v>2.28858423233032</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.44587540626526</v>
+        <v>2.44587516784668</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.48519825935364</v>
+        <v>2.48519802093506</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.50092744827271</v>
+        <v>2.50092697143555</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.45531272888184</v>
+        <v>2.45531225204468</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.46160435676575</v>
+        <v>2.46160459518433</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.57957243919373</v>
+        <v>2.5795726776123</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.61574959754944</v>
+        <v>2.61574935913086</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.61889505386353</v>
+        <v>2.6188952922821</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.58114528656006</v>
+        <v>2.58114552497864</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.25</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.55597901344299</v>
+        <v>2.55597877502441</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.59844756126404</v>
+        <v>2.59844732284546</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.56934881210327</v>
+        <v>2.56934857368469</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.29900002479553</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.59451532363892</v>
+        <v>2.59451508522034</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.61732268333435</v>
+        <v>2.61732244491577</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.61103081703186</v>
+        <v>2.61103057861328</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.63855671882629</v>
+        <v>2.63855695724487</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1351" t="n">
-        <v>2.63934302330017</v>
+        <v>2.63934326171875</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1353" t="n">
-        <v>2.63069248199463</v>
+        <v>2.63069200515747</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.40300011634827</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.67630672454834</v>
+        <v>2.67630648612976</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.64642095565796</v>
+        <v>2.64642119407654</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.45700001716614</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.71877503395081</v>
+        <v>2.71877527236938</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.37700009346008</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.65585899353027</v>
+        <v>2.65585875511169</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.64799427986145</v>
+        <v>2.64799404144287</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.48699998855591</v>
       </c>
       <c r="G1364" t="n">
-        <v>2.7423689365387</v>
+        <v>2.74236869812012</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.74315500259399</v>
+        <v>2.74315524101257</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.52900004386902</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.77539992332458</v>
+        <v>2.77540016174316</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1383" t="n">
-        <v>2.88157153129578</v>
+        <v>2.8815712928772</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1385" t="n">
-        <v>2.89100885391235</v>
+        <v>2.89100861549377</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.66300010681152</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.88078474998474</v>
+        <v>2.88078498840332</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.6029999256134</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.83359742164612</v>
+        <v>2.83359718322754</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.78011894226074</v>
+        <v>2.78011870384216</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G1397" t="n">
-        <v>2.7463014125824</v>
+        <v>2.74630117416382</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.7730405330658</v>
+        <v>2.77304029464722</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G1414" t="n">
-        <v>2.85259461402893</v>
+        <v>2.85259485244751</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.5789999961853</v>
       </c>
       <c r="G1416" t="n">
-        <v>2.90536069869995</v>
+        <v>2.90536093711853</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.91266679763794</v>
+        <v>2.91266655921936</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.59299993515015</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.91672539710999</v>
+        <v>2.91672515869141</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.89561915397644</v>
+        <v>2.89561939239502</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.95569109916687</v>
+        <v>2.95569086074829</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.02388072013855</v>
+        <v>3.02388048171997</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.75300002098083</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.0466103553772</v>
+        <v>3.04661011695862</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.67700004577637</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.98491525650024</v>
+        <v>2.98491501808167</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.00520968437195</v>
+        <v>3.00520944595337</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.99140930175781</v>
+        <v>2.99140954017639</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.99384450912476</v>
+        <v>2.99384474754333</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.90860795974731</v>
+        <v>2.90860772132874</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.59899997711182</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.92159628868103</v>
+        <v>2.92159652709961</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.95650267601013</v>
+        <v>2.95650291442871</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.95325589179993</v>
+        <v>2.95325565338135</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.90860795974731</v>
+        <v>2.90860772132874</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.89643120765686</v>
+        <v>2.89643096923828</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.8493480682373</v>
+        <v>2.84934782981873</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.88750171661377</v>
+        <v>2.88750147819519</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.75680494308472</v>
+        <v>2.75680470466614</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.92078447341919</v>
+        <v>2.92078471183777</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G1481" t="n">
-        <v>2.91266679763794</v>
+        <v>2.91266655921936</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.88750171661377</v>
+        <v>2.88750147819519</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.53699994087219</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.87126612663269</v>
+        <v>2.87126588821411</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.95325589179993</v>
+        <v>2.95325565338135</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.96299695968628</v>
+        <v>2.96299719810486</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.95325589179993</v>
+        <v>2.95325565338135</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.94026708602905</v>
+        <v>2.94026732444763</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.89561915397644</v>
+        <v>2.89561939239502</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.94351434707642</v>
+        <v>2.94351410865784</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.53699994087219</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.87126612663269</v>
+        <v>2.87126588821411</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.54099988937378</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.8745129108429</v>
+        <v>2.87451314926147</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.38700008392334</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.74949884414673</v>
+        <v>2.74949908256531</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.83311223983765</v>
+        <v>2.83311247825623</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.88750171661377</v>
+        <v>2.88750147819519</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.92240810394287</v>
+        <v>2.92240786552429</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.93214964866638</v>
+        <v>2.9321494102478</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.00845670700073</v>
+        <v>3.00845694541931</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1530" t="n">
-        <v>2.89967823028564</v>
+        <v>2.89967846870422</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.89967823028564</v>
+        <v>2.89967846870422</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.91266679763794</v>
+        <v>2.91266655921936</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.5090000629425</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.84853601455688</v>
+        <v>2.84853625297546</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.94676160812378</v>
+        <v>2.94676184654236</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.01576280593872</v>
+        <v>3.01576256752014</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.3989999294281</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.75924038887024</v>
+        <v>2.75924062728882</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.7957706451416</v>
+        <v>2.79577040672302</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.46700000762939</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.81444120407104</v>
+        <v>2.81444096565247</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.80226469039917</v>
+        <v>2.80226492881775</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.375</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.73975729942322</v>
+        <v>2.7397575378418</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.34899997711182</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.71865105628967</v>
+        <v>2.71865129470825</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.81281781196594</v>
+        <v>2.81281805038452</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.64640283584595</v>
+        <v>2.64640307426453</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.75518131256104</v>
+        <v>2.75518155097961</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.75680494308472</v>
+        <v>2.75680470466614</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.95569109916687</v>
+        <v>2.95569086074829</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.95650267601013</v>
+        <v>2.95650291442871</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.5789999961853</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.90536069869995</v>
+        <v>2.90536093711853</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.92078447341919</v>
+        <v>2.92078471183777</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1612" t="n">
-        <v>2.89967823028564</v>
+        <v>2.89967846870422</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.45700001716614</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.80632352828979</v>
+        <v>2.80632376670837</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.8493480682373</v>
+        <v>2.84934782981873</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.86233639717102</v>
+        <v>2.8623366355896</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.81281781196594</v>
+        <v>2.81281805038452</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.38299989700317</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.74625182151794</v>
+        <v>2.74625158309937</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.34800004959106</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.71783971786499</v>
+        <v>2.71783947944641</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.61230826377869</v>
+        <v>2.61230802536011</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.78099989891052</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.25756001472473</v>
+        <v>2.25756025314331</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.81900000572205</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.28840780258179</v>
+        <v>2.28840804100037</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.8529999256134</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.31600856781006</v>
+        <v>2.31600832939148</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>3.64800000190735</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>3216071</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>3.66599988937378</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>3.60400009155273</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>3.64800000190735</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>3.63599991798401</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>3.63599991798401</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>3.53600001335144</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>3.49600005149841</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>2296348</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>3.48399996757507</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>3.5</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>3.48600006103516</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>3027130</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>3.43199992179871</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>3.49000000953674</v>
       </c>
       <c r="D2737" t="n">
-        <v>3.43199992179871</v>
+        <v>3.4300000667572</v>
       </c>
       <c r="E2737" t="n">
         <v>3.48000001907349</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>3.4300000667572</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>2065797</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>3.48600006103516</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>3.41199994087219</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>3.42000007629395</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>3.46000003814697</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>1741921</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>3.45199990272522</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>3.49600005149841</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>2008676</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>3.46399998664856</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>3.46600008010864</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G2" t="n">
-        <v>1.63574457168579</v>
+        <v>1.63574481010437</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G3" t="n">
-        <v>1.63708317279816</v>
+        <v>1.63708329200745</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G4" t="n">
-        <v>1.63440597057343</v>
+        <v>1.63440608978271</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63842177391052</v>
+        <v>1.63842153549194</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65314590930939</v>
+        <v>1.65314614772797</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71605896949768</v>
+        <v>1.71605908870697</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7187362909317</v>
+        <v>1.71873652935028</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67322468757629</v>
+        <v>1.673224568367</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63172852993011</v>
+        <v>1.6317286491394</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G13" t="n">
-        <v>1.69865763187408</v>
+        <v>1.69865775108337</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6919652223587</v>
+        <v>1.69196486473083</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72810661792755</v>
+        <v>1.72810626029968</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75755512714386</v>
+        <v>1.75755524635315</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>1.74015378952026</v>
+        <v>1.7401534318924</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G21" t="n">
-        <v>1.72676801681519</v>
+        <v>1.72676813602448</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G22" t="n">
-        <v>1.77094089984894</v>
+        <v>1.77094078063965</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G23" t="n">
-        <v>1.77763378620148</v>
+        <v>1.77763402462006</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7629097700119</v>
+        <v>1.76290953159332</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G25" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G26" t="n">
-        <v>1.75220108032227</v>
+        <v>1.75220084190369</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G28" t="n">
-        <v>1.6678706407547</v>
+        <v>1.66787040233612</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G29" t="n">
-        <v>1.6852719783783</v>
+        <v>1.68527185916901</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G31" t="n">
-        <v>1.68125629425049</v>
+        <v>1.68125641345978</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G33" t="n">
-        <v>1.70802760124207</v>
+        <v>1.70802795886993</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G34" t="n">
-        <v>1.7187362909317</v>
+        <v>1.71873652935028</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G35" t="n">
-        <v>1.71605896949768</v>
+        <v>1.71605908870697</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G36" t="n">
-        <v>1.70133495330811</v>
+        <v>1.70133471488953</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G38" t="n">
-        <v>1.72275233268738</v>
+        <v>1.7227520942688</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G39" t="n">
-        <v>1.72542929649353</v>
+        <v>1.72542941570282</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G40" t="n">
-        <v>1.74416959285736</v>
+        <v>1.74416935443878</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G41" t="n">
-        <v>1.75353932380676</v>
+        <v>1.75353956222534</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>1.74015378952026</v>
+        <v>1.7401534318924</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>1.71338224411011</v>
+        <v>1.71338212490082</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G44" t="n">
-        <v>1.69062614440918</v>
+        <v>1.69062650203705</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G45" t="n">
-        <v>1.67188608646393</v>
+        <v>1.67188620567322</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65716171264648</v>
+        <v>1.65716195106506</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G48" t="n">
-        <v>1.67054748535156</v>
+        <v>1.67054760456085</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>1.65983891487122</v>
+        <v>1.65983927249908</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G50" t="n">
-        <v>1.68928778171539</v>
+        <v>1.6892876625061</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G51" t="n">
-        <v>1.70401215553284</v>
+        <v>1.70401191711426</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.68661046028137</v>
+        <v>1.68661057949066</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>1.69999599456787</v>
+        <v>1.69999659061432</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>1.72141373157501</v>
+        <v>1.7214138507843</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>1.76023268699646</v>
+        <v>1.76023256778717</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G57" t="n">
-        <v>1.73479914665222</v>
+        <v>1.73479926586151</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.72141373157501</v>
+        <v>1.7214138507843</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G60" t="n">
-        <v>1.77897274494171</v>
+        <v>1.77897250652313</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G61" t="n">
-        <v>1.76558661460876</v>
+        <v>1.76558673381805</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>1.76558661460876</v>
+        <v>1.76558673381805</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75755512714386</v>
+        <v>1.75755524635315</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G64" t="n">
-        <v>1.75220108032227</v>
+        <v>1.75220084190369</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G65" t="n">
-        <v>1.75755512714386</v>
+        <v>1.75755524635315</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G66" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G67" t="n">
-        <v>1.6852719783783</v>
+        <v>1.68527185916901</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69330358505249</v>
+        <v>1.69330370426178</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G69" t="n">
-        <v>1.69062614440918</v>
+        <v>1.69062650203705</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>1.69999599456787</v>
+        <v>1.69999659061432</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G71" t="n">
-        <v>1.69865763187408</v>
+        <v>1.69865775108337</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.69865763187408</v>
+        <v>1.69865775108337</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>1.70668935775757</v>
+        <v>1.70668911933899</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69330358505249</v>
+        <v>1.69330370426178</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.69330358505249</v>
+        <v>1.69330370426178</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G77" t="n">
-        <v>1.70267379283905</v>
+        <v>1.70267367362976</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.5</v>
       </c>
       <c r="G78" t="n">
-        <v>1.67322468757629</v>
+        <v>1.673224568367</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.5</v>
       </c>
       <c r="G79" t="n">
-        <v>1.67322468757629</v>
+        <v>1.673224568367</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G80" t="n">
-        <v>1.70133495330811</v>
+        <v>1.70133471488953</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G81" t="n">
-        <v>1.7053507566452</v>
+        <v>1.70535087585449</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G83" t="n">
-        <v>1.72676801681519</v>
+        <v>1.72676813602448</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G84" t="n">
-        <v>1.75755512714386</v>
+        <v>1.75755524635315</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71605896949768</v>
+        <v>1.71605908870697</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>1.73346090316772</v>
+        <v>1.73346078395844</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G89" t="n">
-        <v>1.73346090316772</v>
+        <v>1.73346078395844</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G91" t="n">
-        <v>1.74416959285736</v>
+        <v>1.74416935443878</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G93" t="n">
-        <v>1.71739745140076</v>
+        <v>1.71739780902863</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>1.73346090316772</v>
+        <v>1.73346078395844</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.71338224411011</v>
+        <v>1.71338212490082</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G98" t="n">
-        <v>1.68259453773499</v>
+        <v>1.68259477615356</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67456352710724</v>
+        <v>1.67456340789795</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>1.70802760124207</v>
+        <v>1.70802795886993</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72542929649353</v>
+        <v>1.72542941570282</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G102" t="n">
-        <v>1.73346090316772</v>
+        <v>1.73346078395844</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G103" t="n">
-        <v>1.74952375888824</v>
+        <v>1.74952387809753</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75353932380676</v>
+        <v>1.75353956222534</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G105" t="n">
-        <v>1.7682638168335</v>
+        <v>1.76826369762421</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>1.74015378952026</v>
+        <v>1.7401534318924</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G107" t="n">
-        <v>1.75487804412842</v>
+        <v>1.75487816333771</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.76692521572113</v>
+        <v>1.76692569255829</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>1.76023268699646</v>
+        <v>1.76023256778717</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G110" t="n">
-        <v>1.74550783634186</v>
+        <v>1.74550807476044</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G111" t="n">
-        <v>1.75621688365936</v>
+        <v>1.75621676445007</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G112" t="n">
-        <v>1.74818527698517</v>
+        <v>1.74818515777588</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G113" t="n">
-        <v>1.74684643745422</v>
+        <v>1.74684655666351</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G114" t="n">
-        <v>1.73747658729553</v>
+        <v>1.73747646808624</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G117" t="n">
-        <v>1.66920924186707</v>
+        <v>1.66920900344849</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>1.63976037502289</v>
+        <v>1.6397602558136</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G119" t="n">
-        <v>1.69330358505249</v>
+        <v>1.69330370426178</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G121" t="n">
-        <v>1.69885528087616</v>
+        <v>1.69885504245758</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G122" t="n">
-        <v>1.66693198680878</v>
+        <v>1.66693222522736</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G124" t="n">
-        <v>1.63223361968994</v>
+        <v>1.63223326206207</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G125" t="n">
-        <v>1.60308647155762</v>
+        <v>1.60308635234833</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G126" t="n">
-        <v>1.63778531551361</v>
+        <v>1.6377854347229</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>1.6655445098877</v>
+        <v>1.66554427146912</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G129" t="n">
-        <v>1.75714910030365</v>
+        <v>1.75714933872223</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G130" t="n">
-        <v>1.73216593265533</v>
+        <v>1.73216605186462</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.5</v>
       </c>
       <c r="G131" t="n">
-        <v>1.7349419593811</v>
+        <v>1.73494184017181</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>1.7099586725235</v>
+        <v>1.70995879173279</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G134" t="n">
-        <v>1.65444076061249</v>
+        <v>1.65444087982178</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G135" t="n">
-        <v>1.686363697052</v>
+        <v>1.68636405467987</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>1.6724841594696</v>
+        <v>1.67248427867889</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>1.6655445098877</v>
+        <v>1.66554427146912</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G138" t="n">
-        <v>1.69607937335968</v>
+        <v>1.69607949256897</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G139" t="n">
-        <v>1.69191539287567</v>
+        <v>1.69191551208496</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G141" t="n">
-        <v>1.69469141960144</v>
+        <v>1.69469153881073</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G142" t="n">
-        <v>1.7002432346344</v>
+        <v>1.70024311542511</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G143" t="n">
-        <v>1.7002432346344</v>
+        <v>1.70024311542511</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G144" t="n">
-        <v>1.7099586725235</v>
+        <v>1.70995879173279</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G145" t="n">
-        <v>1.69885528087616</v>
+        <v>1.69885504245758</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G147" t="n">
-        <v>1.70857095718384</v>
+        <v>1.70857071876526</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.5</v>
       </c>
       <c r="G148" t="n">
-        <v>1.7349419593811</v>
+        <v>1.73494184017181</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>1.759925365448</v>
+        <v>1.75992500782013</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G150" t="n">
-        <v>1.77935636043549</v>
+        <v>1.77935647964478</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75437378883362</v>
+        <v>1.75437331199646</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G156" t="n">
-        <v>1.76686501502991</v>
+        <v>1.76686465740204</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.721062541008</v>
+        <v>1.72106277942657</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G158" t="n">
-        <v>1.74326992034912</v>
+        <v>1.74327003955841</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G160" t="n">
-        <v>1.73216593265533</v>
+        <v>1.73216605186462</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G161" t="n">
-        <v>1.69469141960144</v>
+        <v>1.69469153881073</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G162" t="n">
-        <v>1.7002432346344</v>
+        <v>1.70024311542511</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69885528087616</v>
+        <v>1.69885504245758</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G164" t="n">
-        <v>1.67526006698608</v>
+        <v>1.67525994777679</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>1.67109620571136</v>
+        <v>1.67109608650208</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G166" t="n">
-        <v>1.69330358505249</v>
+        <v>1.69330334663391</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G167" t="n">
-        <v>1.69191539287567</v>
+        <v>1.69191551208496</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G168" t="n">
-        <v>1.70163094997406</v>
+        <v>1.70163118839264</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.7002432346344</v>
+        <v>1.70024311542511</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G170" t="n">
-        <v>1.71551048755646</v>
+        <v>1.71551072597504</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G171" t="n">
-        <v>1.72383856773376</v>
+        <v>1.72383844852448</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.686363697052</v>
+        <v>1.68636405467987</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G173" t="n">
-        <v>1.71134698390961</v>
+        <v>1.71134686470032</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G174" t="n">
-        <v>1.71551048755646</v>
+        <v>1.71551072597504</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G175" t="n">
-        <v>1.71412265300751</v>
+        <v>1.7141227722168</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G176" t="n">
-        <v>1.73910582065582</v>
+        <v>1.73910593986511</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G177" t="n">
-        <v>1.75714910030365</v>
+        <v>1.75714933872223</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G179" t="n">
-        <v>1.68219995498657</v>
+        <v>1.68219947814941</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G180" t="n">
-        <v>1.66276848316193</v>
+        <v>1.66276836395264</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G181" t="n">
-        <v>1.6724841594696</v>
+        <v>1.67248427867889</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G182" t="n">
-        <v>1.66276848316193</v>
+        <v>1.66276836395264</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G184" t="n">
-        <v>1.66415655612946</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G185" t="n">
-        <v>1.68081164360046</v>
+        <v>1.68081188201904</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G186" t="n">
-        <v>1.66415655612946</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G187" t="n">
-        <v>1.68081164360046</v>
+        <v>1.68081188201904</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G188" t="n">
-        <v>1.63917338848114</v>
+        <v>1.63917350769043</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G189" t="n">
-        <v>1.63639748096466</v>
+        <v>1.63639736175537</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63084530830383</v>
+        <v>1.63084554672241</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>1.64472508430481</v>
+        <v>1.6447252035141</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G193" t="n">
-        <v>1.66415655612946</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G194" t="n">
-        <v>1.62529349327087</v>
+        <v>1.62529361248016</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G195" t="n">
-        <v>1.56283605098724</v>
+        <v>1.56283593177795</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G196" t="n">
-        <v>1.53785264492035</v>
+        <v>1.53785276412964</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G197" t="n">
-        <v>1.5253609418869</v>
+        <v>1.52536118030548</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>1.51286971569061</v>
+        <v>1.51286947727203</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G200" t="n">
-        <v>1.54201650619507</v>
+        <v>1.54201638698578</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G201" t="n">
-        <v>1.54618036746979</v>
+        <v>1.5461802482605</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G202" t="n">
-        <v>1.5531200170517</v>
+        <v>1.55312013626099</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G203" t="n">
-        <v>1.56422364711761</v>
+        <v>1.56422388553619</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G204" t="n">
-        <v>1.5503443479538</v>
+        <v>1.55034422874451</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G206" t="n">
-        <v>1.56838762760162</v>
+        <v>1.56838750839233</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G208" t="n">
-        <v>1.55450809001923</v>
+        <v>1.55450820922852</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G209" t="n">
-        <v>1.54756832122803</v>
+        <v>1.54756820201874</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G211" t="n">
-        <v>1.55728387832642</v>
+        <v>1.55728399753571</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G212" t="n">
-        <v>1.5919828414917</v>
+        <v>1.59198260307312</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G213" t="n">
-        <v>1.5989226102829</v>
+        <v>1.59892249107361</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>1.61696588993073</v>
+        <v>1.61696600914001</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>1.60308647155762</v>
+        <v>1.60308635234833</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55450809001923</v>
+        <v>1.55450820922852</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>1.49760210514069</v>
+        <v>1.4976019859314</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>1.47817087173462</v>
+        <v>1.47817075252533</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G222" t="n">
-        <v>1.39905738830566</v>
+        <v>1.39905726909637</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>1.40183317661285</v>
+        <v>1.40183341503143</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G224" t="n">
-        <v>1.38517761230469</v>
+        <v>1.38517773151398</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G225" t="n">
-        <v>1.38448369503021</v>
+        <v>1.3844838142395</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G226" t="n">
-        <v>1.3893415927887</v>
+        <v>1.38934171199799</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G227" t="n">
-        <v>1.36991035938263</v>
+        <v>1.36991012096405</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G228" t="n">
-        <v>1.36227667331696</v>
+        <v>1.36227643489838</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33729338645935</v>
+        <v>1.33729326725006</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G231" t="n">
-        <v>1.34978485107422</v>
+        <v>1.34978497028351</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G234" t="n">
-        <v>1.34284496307373</v>
+        <v>1.34284508228302</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G237" t="n">
-        <v>1.32341384887695</v>
+        <v>1.32341372966766</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G238" t="n">
-        <v>1.30190074443817</v>
+        <v>1.30190062522888</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G239" t="n">
-        <v>1.31924998760223</v>
+        <v>1.31924986839294</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G240" t="n">
-        <v>1.3782377243042</v>
+        <v>1.37823796272278</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40183317661285</v>
+        <v>1.40183341503143</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G242" t="n">
-        <v>1.41848874092102</v>
+        <v>1.41848850250244</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>1.42959213256836</v>
+        <v>1.42959225177765</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G245" t="n">
-        <v>1.46845495700836</v>
+        <v>1.46845507621765</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G246" t="n">
-        <v>1.46290326118469</v>
+        <v>1.4629031419754</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G249" t="n">
-        <v>1.48372232913971</v>
+        <v>1.483722448349</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G254" t="n">
-        <v>1.52397310733795</v>
+        <v>1.52397322654724</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G256" t="n">
-        <v>1.51286971569061</v>
+        <v>1.51286947727203</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G257" t="n">
-        <v>1.52119708061218</v>
+        <v>1.52119731903076</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53785264492035</v>
+        <v>1.53785276412964</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G260" t="n">
-        <v>1.52952480316162</v>
+        <v>1.52952492237091</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G261" t="n">
-        <v>1.53230094909668</v>
+        <v>1.53230082988739</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G262" t="n">
-        <v>1.52119708061218</v>
+        <v>1.52119731903076</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G263" t="n">
-        <v>1.49899005889893</v>
+        <v>1.49899017810822</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G266" t="n">
-        <v>1.5989226102829</v>
+        <v>1.59892249107361</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>1.58226716518402</v>
+        <v>1.58226704597473</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>1.58226716518402</v>
+        <v>1.58226704597473</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57255160808563</v>
+        <v>1.57255172729492</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G270" t="n">
-        <v>1.58365511894226</v>
+        <v>1.58365499973297</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G271" t="n">
-        <v>1.58504319190979</v>
+        <v>1.58504283428192</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G273" t="n">
-        <v>1.57116341590881</v>
+        <v>1.5711635351181</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G274" t="n">
-        <v>1.5919828414917</v>
+        <v>1.59198260307312</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G275" t="n">
-        <v>1.56838762760162</v>
+        <v>1.56838750839233</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G277" t="n">
-        <v>1.55728387832642</v>
+        <v>1.55728399753571</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G279" t="n">
-        <v>1.49760210514069</v>
+        <v>1.4976019859314</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G280" t="n">
-        <v>1.51286971569061</v>
+        <v>1.51286947727203</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G282" t="n">
-        <v>1.51286971569061</v>
+        <v>1.51286947727203</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G283" t="n">
-        <v>1.48649823665619</v>
+        <v>1.48649835586548</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>1.56838762760162</v>
+        <v>1.56838750839233</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.58226716518402</v>
+        <v>1.58226704597473</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G291" t="n">
-        <v>1.61141407489777</v>
+        <v>1.61141431331635</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="n">
-        <v>1.59614670276642</v>
+        <v>1.59614682197571</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G293" t="n">
-        <v>1.60725009441376</v>
+        <v>1.60725033283234</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>1.63084530830383</v>
+        <v>1.63084554672241</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G295" t="n">
-        <v>1.63639748096466</v>
+        <v>1.63639736175537</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G296" t="n">
-        <v>1.61974191665649</v>
+        <v>1.61974215507507</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G297" t="n">
-        <v>1.62251794338226</v>
+        <v>1.62251806259155</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G299" t="n">
-        <v>1.62390553951263</v>
+        <v>1.62390565872192</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G300" t="n">
-        <v>1.63778531551361</v>
+        <v>1.6377854347229</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G301" t="n">
-        <v>1.64194893836975</v>
+        <v>1.64194905757904</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>1.64472508430481</v>
+        <v>1.6447252035141</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G303" t="n">
-        <v>1.65721678733826</v>
+        <v>1.65721654891968</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G304" t="n">
-        <v>1.6613804101944</v>
+        <v>1.66138052940369</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G305" t="n">
-        <v>1.64750099182129</v>
+        <v>1.64750134944916</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>1.65166521072388</v>
+        <v>1.6516649723053</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G307" t="n">
-        <v>1.64333713054657</v>
+        <v>1.64333689212799</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G308" t="n">
-        <v>1.64611315727234</v>
+        <v>1.64611303806305</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G310" t="n">
-        <v>1.66415655612946</v>
+        <v>1.66415667533875</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>1.70718324184418</v>
+        <v>1.7071830034256</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G312" t="n">
-        <v>1.71273481845856</v>
+        <v>1.71273469924927</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75298523902893</v>
+        <v>1.75298571586609</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>1.79046022891998</v>
+        <v>1.79046034812927</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>1.79046022891998</v>
+        <v>1.79046034812927</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G317" t="n">
-        <v>1.81960701942444</v>
+        <v>1.81960725784302</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G318" t="n">
-        <v>1.83348667621613</v>
+        <v>1.83348655700684</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G319" t="n">
-        <v>1.83487462997437</v>
+        <v>1.83487486839294</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G322" t="n">
-        <v>1.80989134311676</v>
+        <v>1.80989158153534</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G323" t="n">
-        <v>1.82099545001984</v>
+        <v>1.82099521160126</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G324" t="n">
-        <v>1.82515919208527</v>
+        <v>1.82515907287598</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G325" t="n">
-        <v>1.83487462997437</v>
+        <v>1.83487486839294</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.83487462997437</v>
+        <v>1.83487486839294</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G327" t="n">
-        <v>1.83487462997437</v>
+        <v>1.83487486839294</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G328" t="n">
-        <v>1.83209872245789</v>
+        <v>1.83209919929504</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G329" t="n">
-        <v>1.86263406276703</v>
+        <v>1.86263382434845</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G330" t="n">
-        <v>1.85569417476654</v>
+        <v>1.85569405555725</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G331" t="n">
-        <v>1.83209872245789</v>
+        <v>1.83209919929504</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G332" t="n">
-        <v>1.83487462997437</v>
+        <v>1.83487486839294</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G333" t="n">
-        <v>1.80017578601837</v>
+        <v>1.80017614364624</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G334" t="n">
-        <v>1.79046022891998</v>
+        <v>1.79046034812927</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>1.80433976650238</v>
+        <v>1.80433928966522</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G336" t="n">
-        <v>1.8473664522171</v>
+        <v>1.84736621379852</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>1.8182190656662</v>
+        <v>1.81821930408478</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>1.80850374698639</v>
+        <v>1.8085036277771</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G339" t="n">
-        <v>1.82099545001984</v>
+        <v>1.82099521160126</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G340" t="n">
-        <v>1.82238292694092</v>
+        <v>1.82238304615021</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G341" t="n">
-        <v>1.8362625837326</v>
+        <v>1.83626246452332</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G342" t="n">
-        <v>1.84320223331451</v>
+        <v>1.8432023525238</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G343" t="n">
-        <v>1.85430598258972</v>
+        <v>1.8543062210083</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G345" t="n">
-        <v>1.86679768562317</v>
+        <v>1.86679792404175</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G346" t="n">
-        <v>1.91121196746826</v>
+        <v>1.91121220588684</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G348" t="n">
-        <v>1.97089397907257</v>
+        <v>1.97089421749115</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G349" t="n">
-        <v>1.98199772834778</v>
+        <v>1.98199808597565</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G350" t="n">
-        <v>1.9653422832489</v>
+        <v>1.96534276008606</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>1.97783386707306</v>
+        <v>1.97783410549164</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>1.98616170883179</v>
+        <v>1.98616147041321</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G355" t="n">
-        <v>1.99865353107452</v>
+        <v>1.99865305423737</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G356" t="n">
-        <v>2.03890371322632</v>
+        <v>2.03890419006348</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G357" t="n">
-        <v>2.02363610267639</v>
+        <v>2.02363634109497</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>2.02224826812744</v>
+        <v>2.02224850654602</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>2.01253271102905</v>
+        <v>2.01253294944763</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G360" t="n">
-        <v>1.96811842918396</v>
+        <v>1.96811830997467</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G362" t="n">
-        <v>2.03335213661194</v>
+        <v>2.03335189819336</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="n">
-        <v>1.99865353107452</v>
+        <v>1.99865305423737</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G365" t="n">
-        <v>1.98616170883179</v>
+        <v>1.98616147041321</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G366" t="n">
-        <v>2.01530885696411</v>
+        <v>2.01530838012695</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>2.01253271102905</v>
+        <v>2.01253294944763</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G368" t="n">
-        <v>2.03057599067688</v>
+        <v>2.03057622909546</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G369" t="n">
-        <v>2.01947283744812</v>
+        <v>2.01947259902954</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>2.05694723129272</v>
+        <v>2.0569474697113</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>2.06388711929321</v>
+        <v>2.06388688087463</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G377" t="n">
-        <v>2.08101892471313</v>
+        <v>2.08101844787598</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G378" t="n">
-        <v>2.06527519226074</v>
+        <v>2.06527495384216</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G380" t="n">
-        <v>2.02376937866211</v>
+        <v>2.02376914024353</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G381" t="n">
-        <v>1.98512589931488</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G384" t="n">
-        <v>1.91499531269073</v>
+        <v>1.91499543190002</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G386" t="n">
-        <v>1.92358219623566</v>
+        <v>1.92358255386353</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G387" t="n">
-        <v>1.9135639667511</v>
+        <v>1.91356420516968</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G388" t="n">
-        <v>1.86919581890106</v>
+        <v>1.86919569969177</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G389" t="n">
-        <v>1.8878014087677</v>
+        <v>1.88780200481415</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G390" t="n">
-        <v>1.92072021961212</v>
+        <v>1.92071998119354</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G391" t="n">
-        <v>1.89925181865692</v>
+        <v>1.89925158023834</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G392" t="n">
-        <v>1.91499531269073</v>
+        <v>1.91499543190002</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96651935577393</v>
+        <v>1.9665195941925</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G396" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G397" t="n">
-        <v>1.95936334133148</v>
+        <v>1.95936346054077</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>1.98941946029663</v>
+        <v>1.98941957950592</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G401" t="n">
-        <v>1.98512589931488</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G402" t="n">
-        <v>1.98941946029663</v>
+        <v>1.98941957950592</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G403" t="n">
-        <v>1.94791352748871</v>
+        <v>1.94791376590729</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G404" t="n">
-        <v>1.9293075799942</v>
+        <v>1.92930781841278</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.75</v>
       </c>
       <c r="G406" t="n">
-        <v>1.96795094013214</v>
+        <v>1.96795117855072</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G407" t="n">
-        <v>1.957932472229</v>
+        <v>1.95793271064758</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G408" t="n">
-        <v>1.95650136470795</v>
+        <v>1.95650112628937</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G409" t="n">
-        <v>1.95077610015869</v>
+        <v>1.95077633857727</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G410" t="n">
-        <v>1.96222591400146</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G413" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G414" t="n">
-        <v>1.91785788536072</v>
+        <v>1.91785800457001</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G415" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.75</v>
       </c>
       <c r="G416" t="n">
-        <v>1.96795094013214</v>
+        <v>1.96795117855072</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G417" t="n">
-        <v>1.96651935577393</v>
+        <v>1.9665195941925</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G419" t="n">
-        <v>1.96938216686249</v>
+        <v>1.96938240528107</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>1.94934499263763</v>
+        <v>1.94934475421906</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G422" t="n">
-        <v>1.92358219623566</v>
+        <v>1.92358255386353</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>1.91070175170898</v>
+        <v>1.91070163249969</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G424" t="n">
-        <v>1.89209520816803</v>
+        <v>1.89209532737732</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G426" t="n">
-        <v>1.88493919372559</v>
+        <v>1.88493895530701</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G427" t="n">
-        <v>1.92358219623566</v>
+        <v>1.92358255386353</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G428" t="n">
-        <v>1.94075763225555</v>
+        <v>1.94075787067413</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G431" t="n">
-        <v>1.91928911209106</v>
+        <v>1.91928887367249</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G432" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G433" t="n">
-        <v>1.957932472229</v>
+        <v>1.95793271064758</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G434" t="n">
-        <v>1.99085068702698</v>
+        <v>1.99085092544556</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G435" t="n">
-        <v>1.96222591400146</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G436" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.91928911209106</v>
+        <v>1.91928887367249</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G439" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G440" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G441" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360137939453</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G442" t="n">
-        <v>1.92358219623566</v>
+        <v>1.92358255386353</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G443" t="n">
-        <v>1.91642665863037</v>
+        <v>1.91642653942108</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G445" t="n">
-        <v>1.94791352748871</v>
+        <v>1.94791376590729</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G447" t="n">
-        <v>1.90211427211761</v>
+        <v>1.90211403369904</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G448" t="n">
-        <v>1.90354549884796</v>
+        <v>1.90354514122009</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G449" t="n">
-        <v>1.91785788536072</v>
+        <v>1.91785800457001</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>1.91785788536072</v>
+        <v>1.91785800457001</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G451" t="n">
-        <v>1.88923263549805</v>
+        <v>1.88923311233521</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>1.88923263549805</v>
+        <v>1.88923311233521</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G454" t="n">
-        <v>1.93646395206451</v>
+        <v>1.93646371364594</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G456" t="n">
-        <v>1.95220744609833</v>
+        <v>1.95220696926117</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G459" t="n">
-        <v>1.98369467258453</v>
+        <v>1.98369491100311</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G460" t="n">
-        <v>1.957932472229</v>
+        <v>1.95793271064758</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.75</v>
       </c>
       <c r="G462" t="n">
-        <v>1.96795094013214</v>
+        <v>1.96795117855072</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G463" t="n">
-        <v>1.98655724525452</v>
+        <v>1.98655700683594</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="n">
-        <v>1.98512589931488</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G468" t="n">
-        <v>1.98798835277557</v>
+        <v>1.98798859119415</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G469" t="n">
-        <v>1.98941946029663</v>
+        <v>1.98941957950592</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G471" t="n">
-        <v>1.98798835277557</v>
+        <v>1.98798859119415</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G478" t="n">
-        <v>2.1039183139801</v>
+        <v>2.10391855239868</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G479" t="n">
-        <v>2.0953311920166</v>
+        <v>2.09533095359802</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G480" t="n">
-        <v>2.0953311920166</v>
+        <v>2.09533095359802</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.07529401779175</v>
+        <v>2.07529354095459</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G483" t="n">
-        <v>2.07958722114563</v>
+        <v>2.07958745956421</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G486" t="n">
-        <v>2.08101892471313</v>
+        <v>2.08101844787598</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G487" t="n">
-        <v>2.0953311920166</v>
+        <v>2.09533095359802</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G488" t="n">
-        <v>2.10105609893799</v>
+        <v>2.10105633735657</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G489" t="n">
-        <v>2.10248732566833</v>
+        <v>2.10248708724976</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G490" t="n">
-        <v>2.13111209869385</v>
+        <v>2.13111186027527</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G492" t="n">
-        <v>2.16116762161255</v>
+        <v>2.16116809844971</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G493" t="n">
-        <v>2.16403031349182</v>
+        <v>2.1640305519104</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G494" t="n">
-        <v>2.1854989528656</v>
+        <v>2.18549871444702</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G496" t="n">
-        <v>2.20839905738831</v>
+        <v>2.20839881896973</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20410513877869</v>
+        <v>2.20410490036011</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G499" t="n">
-        <v>2.20839905738831</v>
+        <v>2.20839881896973</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G500" t="n">
-        <v>2.19265484809875</v>
+        <v>2.19265556335449</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G501" t="n">
-        <v>2.17834281921387</v>
+        <v>2.17834258079529</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>2.16116762161255</v>
+        <v>2.16116809844971</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G503" t="n">
-        <v>2.20696783065796</v>
+        <v>2.20696759223938</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G505" t="n">
-        <v>2.1597363948822</v>
+        <v>2.15973663330078</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.18263673782349</v>
+        <v>2.18263649940491</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G508" t="n">
-        <v>2.13540577888489</v>
+        <v>2.13540554046631</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G509" t="n">
-        <v>2.13254356384277</v>
+        <v>2.13254332542419</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>2.1253867149353</v>
+        <v>2.12538719177246</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G511" t="n">
-        <v>2.08245015144348</v>
+        <v>2.0824499130249</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G512" t="n">
-        <v>2.10248732566833</v>
+        <v>2.10248708724976</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G513" t="n">
-        <v>2.06384420394897</v>
+        <v>2.0638439655304</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>2.11823105812073</v>
+        <v>2.11823129653931</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G515" t="n">
-        <v>2.16546177864075</v>
+        <v>2.16546201705933</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>2.20410513877869</v>
+        <v>2.20410490036011</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G517" t="n">
-        <v>2.21412396430969</v>
+        <v>2.21412372589111</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G519" t="n">
-        <v>2.17404890060425</v>
+        <v>2.17404913902283</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G522" t="n">
-        <v>2.13540577888489</v>
+        <v>2.13540554046631</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G523" t="n">
-        <v>2.17404890060425</v>
+        <v>2.17404913902283</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G524" t="n">
-        <v>2.18120527267456</v>
+        <v>2.18120551109314</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G526" t="n">
-        <v>2.20267367362976</v>
+        <v>2.20267391204834</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G528" t="n">
-        <v>2.18120527267456</v>
+        <v>2.18120551109314</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G529" t="n">
-        <v>2.15258049964905</v>
+        <v>2.15258073806763</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G530" t="n">
-        <v>2.18406796455383</v>
+        <v>2.18406772613525</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G532" t="n">
-        <v>2.10248732566833</v>
+        <v>2.10248708724976</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.1039183139801</v>
+        <v>2.10391855239868</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G534" t="n">
-        <v>2.1253867149353</v>
+        <v>2.12538719177246</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G535" t="n">
-        <v>2.09246850013733</v>
+        <v>2.09246897697449</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G536" t="n">
-        <v>2.08245015144348</v>
+        <v>2.0824499130249</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G538" t="n">
-        <v>2.08245015144348</v>
+        <v>2.0824499130249</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G539" t="n">
-        <v>2.02233815193176</v>
+        <v>2.02233791351318</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G540" t="n">
-        <v>1.98655724525452</v>
+        <v>1.98655700683594</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G541" t="n">
-        <v>1.98798835277557</v>
+        <v>1.98798859119415</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G543" t="n">
-        <v>1.97081351280212</v>
+        <v>1.97081327438354</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G544" t="n">
-        <v>1.94362020492554</v>
+        <v>1.94362008571625</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.75</v>
       </c>
       <c r="G547" t="n">
-        <v>1.96795094013214</v>
+        <v>1.96795117855072</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>1.9293075799942</v>
+        <v>1.92930781841278</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.75</v>
       </c>
       <c r="G549" t="n">
-        <v>1.96795094013214</v>
+        <v>1.96795117855072</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G551" t="n">
-        <v>2.03665041923523</v>
+        <v>2.03665018081665</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G552" t="n">
-        <v>2.04380631446838</v>
+        <v>2.04380679130554</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G554" t="n">
-        <v>1.98798835277557</v>
+        <v>1.98798859119415</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G555" t="n">
-        <v>1.95077610015869</v>
+        <v>1.95077633857727</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G556" t="n">
-        <v>1.96222591400146</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>1.98226380348206</v>
+        <v>1.9822633266449</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G558" t="n">
-        <v>1.96222591400146</v>
+        <v>1.96222639083862</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G559" t="n">
-        <v>1.98512589931488</v>
+        <v>1.9851256608963</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G561" t="n">
-        <v>1.95507001876831</v>
+        <v>1.95506978034973</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G562" t="n">
-        <v>1.99800705909729</v>
+        <v>1.99800729751587</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G563" t="n">
-        <v>1.99514436721802</v>
+        <v>1.9951446056366</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G564" t="n">
-        <v>1.99371337890625</v>
+        <v>1.99371314048767</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G565" t="n">
-        <v>1.99514436721802</v>
+        <v>1.9951446056366</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G566" t="n">
-        <v>1.98798835277557</v>
+        <v>1.98798859119415</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>1.98226380348206</v>
+        <v>1.9822633266449</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G569" t="n">
-        <v>2.00945711135864</v>
+        <v>2.00945734977722</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G572" t="n">
-        <v>2.03092527389526</v>
+        <v>2.03092551231384</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G573" t="n">
-        <v>2.1196620464325</v>
+        <v>2.11966228485107</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G574" t="n">
-        <v>2.12824964523315</v>
+        <v>2.128249168396</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>2.13683724403381</v>
+        <v>2.13683700561523</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G576" t="n">
-        <v>2.14828729629517</v>
+        <v>2.14828705787659</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G577" t="n">
-        <v>2.13540577888489</v>
+        <v>2.13540554046631</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G578" t="n">
-        <v>2.1597363948822</v>
+        <v>2.15973663330078</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G579" t="n">
-        <v>2.16832423210144</v>
+        <v>2.16832399368286</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G580" t="n">
-        <v>2.17404890060425</v>
+        <v>2.17404913902283</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16116762161255</v>
+        <v>2.16116809844971</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G585" t="n">
-        <v>2.17834281921387</v>
+        <v>2.17834258079529</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G586" t="n">
-        <v>2.16116762161255</v>
+        <v>2.16116809844971</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G587" t="n">
-        <v>2.16403031349182</v>
+        <v>2.1640305519104</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G589" t="n">
-        <v>2.15830540657043</v>
+        <v>2.15830564498901</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G593" t="n">
-        <v>2.20124268531799</v>
+        <v>2.20124244689941</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G596" t="n">
-        <v>2.19265484809875</v>
+        <v>2.19265556335449</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G600" t="n">
-        <v>2.18263673782349</v>
+        <v>2.18263649940491</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G601" t="n">
-        <v>2.13397479057312</v>
+        <v>2.13397455215454</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G602" t="n">
-        <v>2.13111209869385</v>
+        <v>2.13111186027527</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G603" t="n">
-        <v>2.15687417984009</v>
+        <v>2.15687394142151</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G604" t="n">
-        <v>2.13111209869385</v>
+        <v>2.13111186027527</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G605" t="n">
-        <v>2.03092527389526</v>
+        <v>2.03092551231384</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G610" t="n">
-        <v>2.03092527389526</v>
+        <v>2.03092551231384</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G611" t="n">
-        <v>2.03235650062561</v>
+        <v>2.03235673904419</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.75</v>
       </c>
       <c r="G612" t="n">
-        <v>1.96795094013214</v>
+        <v>1.96795117855072</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G616" t="n">
-        <v>1.89782047271729</v>
+        <v>1.89782023429871</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G617" t="n">
-        <v>1.88637053966522</v>
+        <v>1.88637042045593</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G618" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360137939453</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G619" t="n">
-        <v>1.94648265838623</v>
+        <v>1.94648241996765</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G620" t="n">
-        <v>1.95220744609833</v>
+        <v>1.95220696926117</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G621" t="n">
-        <v>1.89495754241943</v>
+        <v>1.8949579000473</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G622" t="n">
-        <v>1.86633348464966</v>
+        <v>1.86633336544037</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G623" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360137939453</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G624" t="n">
-        <v>1.93646395206451</v>
+        <v>1.93646371364594</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G627" t="n">
-        <v>1.93360114097595</v>
+        <v>1.93360137939453</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G630" t="n">
-        <v>1.98477816581726</v>
+        <v>1.98477840423584</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>2.01741313934326</v>
+        <v>2.01741290092468</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G640" t="n">
-        <v>2.04559707641602</v>
+        <v>2.04559731483459</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>2.06933164596558</v>
+        <v>2.069331407547</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G643" t="n">
-        <v>2.05449771881104</v>
+        <v>2.05449795722961</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.01741313934326</v>
+        <v>2.01741290092468</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G646" t="n">
-        <v>2.05746459960938</v>
+        <v>2.0574643611908</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G647" t="n">
-        <v>2.044114112854</v>
+        <v>2.04411387443542</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G648" t="n">
-        <v>2.044114112854</v>
+        <v>2.04411387443542</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G649" t="n">
-        <v>2.07674813270569</v>
+        <v>2.07674837112427</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G653" t="n">
-        <v>2.04559707641602</v>
+        <v>2.04559731483459</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G654" t="n">
-        <v>2.01592946052551</v>
+        <v>2.01592922210693</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>2.07674813270569</v>
+        <v>2.07674837112427</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>2.07674813270569</v>
+        <v>2.07674837112427</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G664" t="n">
-        <v>2.12421703338623</v>
+        <v>2.12421727180481</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G665" t="n">
-        <v>2.12273359298706</v>
+        <v>2.12273383140564</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G666" t="n">
-        <v>2.09158205986023</v>
+        <v>2.09158277511597</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G672" t="n">
-        <v>2.03076314926147</v>
+        <v>2.03076338768005</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G673" t="n">
-        <v>2.07526540756226</v>
+        <v>2.0752649307251</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G675" t="n">
-        <v>2.06636476516724</v>
+        <v>2.06636500358582</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G680" t="n">
-        <v>2.00257897377014</v>
+        <v>2.00257921218872</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G691" t="n">
-        <v>2.10938310623169</v>
+        <v>2.10938334465027</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G693" t="n">
-        <v>2.11828374862671</v>
+        <v>2.11828351020813</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>2.08416557312012</v>
+        <v>2.08416533470154</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>2.06933164596558</v>
+        <v>2.069331407547</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G696" t="n">
-        <v>2.044114112854</v>
+        <v>2.04411387443542</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G697" t="n">
-        <v>2.03224635124207</v>
+        <v>2.03224658966064</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G698" t="n">
-        <v>2.03224635124207</v>
+        <v>2.03224658966064</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01592946052551</v>
+        <v>2.01592922210693</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G702" t="n">
-        <v>1.98477816581726</v>
+        <v>1.98477840423584</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G706" t="n">
-        <v>1.92989265918732</v>
+        <v>1.9298928976059</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G707" t="n">
-        <v>1.87945759296417</v>
+        <v>1.87945735454559</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>1.89874160289764</v>
+        <v>1.89874148368835</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85572326183319</v>
+        <v>1.85572338104248</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G710" t="n">
-        <v>1.85572326183319</v>
+        <v>1.85572338104248</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G713" t="n">
-        <v>1.83495581150055</v>
+        <v>1.83495569229126</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G714" t="n">
-        <v>1.79342067241669</v>
+        <v>1.79342079162598</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G715" t="n">
-        <v>1.81418812274933</v>
+        <v>1.81418824195862</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G716" t="n">
-        <v>1.82160532474518</v>
+        <v>1.82160556316376</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79342067241669</v>
+        <v>1.79342079162598</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G719" t="n">
-        <v>1.78155338764191</v>
+        <v>1.78155362606049</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G720" t="n">
-        <v>1.84682273864746</v>
+        <v>1.84682309627533</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G721" t="n">
-        <v>1.81715488433838</v>
+        <v>1.81715476512909</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G722" t="n">
-        <v>1.81122124195099</v>
+        <v>1.81122136116028</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G723" t="n">
-        <v>1.80083775520325</v>
+        <v>1.80083763599396</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G725" t="n">
-        <v>1.80825459957123</v>
+        <v>1.80825448036194</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>1.82457220554352</v>
+        <v>1.82457196712494</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G727" t="n">
-        <v>1.80083775520325</v>
+        <v>1.80083763599396</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G728" t="n">
-        <v>1.84088945388794</v>
+        <v>1.84088921546936</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G729" t="n">
-        <v>1.88390755653381</v>
+        <v>1.8839076757431</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G730" t="n">
-        <v>1.83792245388031</v>
+        <v>1.83792221546173</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G731" t="n">
-        <v>1.89577484130859</v>
+        <v>1.89577496051788</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G732" t="n">
-        <v>1.88687431812286</v>
+        <v>1.88687443733215</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G733" t="n">
-        <v>1.89429116249084</v>
+        <v>1.89429128170013</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G735" t="n">
-        <v>1.84978997707367</v>
+        <v>1.84978950023651</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G736" t="n">
-        <v>1.8438560962677</v>
+        <v>1.84385585784912</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.83940589427948</v>
+        <v>1.8394056558609</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G738" t="n">
-        <v>1.83495581150055</v>
+        <v>1.83495569229126</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G740" t="n">
-        <v>1.81270468235016</v>
+        <v>1.81270503997803</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G742" t="n">
-        <v>1.84682273864746</v>
+        <v>1.84682309627533</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G743" t="n">
-        <v>1.84682273864746</v>
+        <v>1.84682309627533</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G744" t="n">
-        <v>1.82902216911316</v>
+        <v>1.82902204990387</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G746" t="n">
-        <v>1.79935419559479</v>
+        <v>1.79935443401337</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G747" t="n">
-        <v>1.84978997707367</v>
+        <v>1.84978950023651</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G749" t="n">
-        <v>1.83495581150055</v>
+        <v>1.83495569229126</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G751" t="n">
-        <v>1.80825459957123</v>
+        <v>1.80825448036194</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G752" t="n">
-        <v>1.79045391082764</v>
+        <v>1.79045403003693</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G753" t="n">
-        <v>1.86610674858093</v>
+        <v>1.8661071062088</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G756" t="n">
-        <v>2.00554609298706</v>
+        <v>2.00554537773132</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G758" t="n">
-        <v>1.97884452342987</v>
+        <v>1.97884476184845</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>2.00999593734741</v>
+        <v>2.00999617576599</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>2.00257897377014</v>
+        <v>2.00257921218872</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>2.05449771881104</v>
+        <v>2.05449795722961</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G762" t="n">
-        <v>1.99516201019287</v>
+        <v>1.99516177177429</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G764" t="n">
-        <v>2.01592946052551</v>
+        <v>2.01592922210693</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G766" t="n">
-        <v>2.09899926185608</v>
+        <v>2.09899950027466</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G770" t="n">
-        <v>2.07674813270569</v>
+        <v>2.07674837112427</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G772" t="n">
-        <v>2.10938310623169</v>
+        <v>2.10938334465027</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G774" t="n">
-        <v>2.13608455657959</v>
+        <v>2.13608431816101</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G779" t="n">
-        <v>2.12421703338623</v>
+        <v>2.12421727180481</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G782" t="n">
-        <v>2.12421703338623</v>
+        <v>2.12421727180481</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G786" t="n">
-        <v>2.19690322875977</v>
+        <v>2.19690346717834</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>2.1880030632019</v>
+        <v>2.18800282478333</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G789" t="n">
-        <v>2.19393658638</v>
+        <v>2.19393634796143</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G790" t="n">
-        <v>2.17465233802795</v>
+        <v>2.17465209960938</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G791" t="n">
-        <v>2.16130185127258</v>
+        <v>2.16130208969116</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G792" t="n">
-        <v>2.18503642082214</v>
+        <v>2.18503594398499</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G794" t="n">
-        <v>2.20431995391846</v>
+        <v>2.20432019233704</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G796" t="n">
-        <v>2.20135354995728</v>
+        <v>2.2013533115387</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G799" t="n">
-        <v>2.17465233802795</v>
+        <v>2.17465209960938</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G800" t="n">
-        <v>2.19690322875977</v>
+        <v>2.19690346717834</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G801" t="n">
-        <v>2.22657108306885</v>
+        <v>2.22657132148743</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G802" t="n">
-        <v>2.1954197883606</v>
+        <v>2.19542002677917</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G807" t="n">
-        <v>2.18503642082214</v>
+        <v>2.18503594398499</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G808" t="n">
-        <v>2.20283675193787</v>
+        <v>2.20283699035645</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G809" t="n">
-        <v>2.19987034797668</v>
+        <v>2.19987010955811</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G812" t="n">
-        <v>2.20135354995728</v>
+        <v>2.2013533115387</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G813" t="n">
-        <v>2.19987034797668</v>
+        <v>2.19987010955811</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G814" t="n">
-        <v>2.17465233802795</v>
+        <v>2.17465209960938</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G816" t="n">
-        <v>2.14498424530029</v>
+        <v>2.14498448371887</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G817" t="n">
-        <v>2.24585556983948</v>
+        <v>2.2458553314209</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G818" t="n">
-        <v>2.27997303009033</v>
+        <v>2.27997326850891</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G819" t="n">
-        <v>2.28145670890808</v>
+        <v>2.2814564704895</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G820" t="n">
-        <v>2.30222415924072</v>
+        <v>2.3022243976593</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G821" t="n">
-        <v>2.32595801353455</v>
+        <v>2.32595825195312</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>2.32892465591431</v>
+        <v>2.32892513275146</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G824" t="n">
-        <v>2.38974404335022</v>
+        <v>2.38974380493164</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G825" t="n">
-        <v>2.38529396057129</v>
+        <v>2.38529419898987</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G826" t="n">
-        <v>2.39122748374939</v>
+        <v>2.39122724533081</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G828" t="n">
-        <v>2.44166278839111</v>
+        <v>2.44166302680969</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G830" t="n">
-        <v>2.39716172218323</v>
+        <v>2.39716124534607</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G832" t="n">
-        <v>2.39716172218323</v>
+        <v>2.39716124534607</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>2.39122748374939</v>
+        <v>2.39122724533081</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G835" t="n">
-        <v>2.39716172218323</v>
+        <v>2.39716124534607</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G837" t="n">
-        <v>2.3749098777771</v>
+        <v>2.37491011619568</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G839" t="n">
-        <v>2.33189177513123</v>
+        <v>2.3318920135498</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G840" t="n">
-        <v>2.34672570228577</v>
+        <v>2.34672594070435</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G845" t="n">
-        <v>2.34375905990601</v>
+        <v>2.34375929832458</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G848" t="n">
-        <v>2.35562658309937</v>
+        <v>2.35562610626221</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G849" t="n">
-        <v>2.32447481155396</v>
+        <v>2.32447504997253</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G851" t="n">
-        <v>2.32447481155396</v>
+        <v>2.32447504997253</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G852" t="n">
-        <v>2.32744169235229</v>
+        <v>2.32744145393372</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G853" t="n">
-        <v>2.38232731819153</v>
+        <v>2.38232707977295</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G854" t="n">
-        <v>2.38529396057129</v>
+        <v>2.38529419898987</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G856" t="n">
-        <v>2.43127942085266</v>
+        <v>2.43127918243408</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G857" t="n">
-        <v>2.43424606323242</v>
+        <v>2.43424582481384</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G861" t="n">
-        <v>2.42979598045349</v>
+        <v>2.42979574203491</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G867" t="n">
-        <v>2.38974404335022</v>
+        <v>2.38974380493164</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G870" t="n">
-        <v>2.42979598045349</v>
+        <v>2.42979574203491</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G871" t="n">
-        <v>2.45649695396423</v>
+        <v>2.45649671554565</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G872" t="n">
-        <v>2.48171448707581</v>
+        <v>2.48171424865723</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G874" t="n">
-        <v>2.49506497383118</v>
+        <v>2.49506521224976</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G875" t="n">
-        <v>2.49061465263367</v>
+        <v>2.49061489105225</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>2.47726392745972</v>
+        <v>2.47726440429688</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53511667251587</v>
+        <v>2.53511643409729</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G881" t="n">
-        <v>2.54105019569397</v>
+        <v>2.54105067253113</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G883" t="n">
-        <v>2.60186958312988</v>
+        <v>2.60186910629272</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G887" t="n">
-        <v>2.53926539421082</v>
+        <v>2.53926563262939</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G888" t="n">
-        <v>2.56827688217163</v>
+        <v>2.56827735900879</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G892" t="n">
-        <v>2.69043016433716</v>
+        <v>2.69043064117432</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G894" t="n">
-        <v>2.65683841705322</v>
+        <v>2.65683817863464</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G895" t="n">
-        <v>2.66600012779236</v>
+        <v>2.66599988937378</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G896" t="n">
-        <v>2.67974209785461</v>
+        <v>2.67974233627319</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G897" t="n">
-        <v>2.67821550369263</v>
+        <v>2.67821502685547</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G898" t="n">
-        <v>2.67821550369263</v>
+        <v>2.67821502685547</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G899" t="n">
-        <v>2.70875382423401</v>
+        <v>2.70875358581543</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G901" t="n">
-        <v>2.68890404701233</v>
+        <v>2.68890380859375</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G902" t="n">
-        <v>2.70875382423401</v>
+        <v>2.70875358581543</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G905" t="n">
-        <v>2.62935352325439</v>
+        <v>2.62935376167297</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>2.63393449783325</v>
+        <v>2.63393473625183</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G909" t="n">
-        <v>2.61866545677185</v>
+        <v>2.61866521835327</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G912" t="n">
-        <v>2.62171936035156</v>
+        <v>2.62171912193298</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>2.61866545677185</v>
+        <v>2.61866521835327</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G917" t="n">
-        <v>2.61255764961243</v>
+        <v>2.61255741119385</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G922" t="n">
-        <v>2.6461501121521</v>
+        <v>2.64614987373352</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G924" t="n">
-        <v>2.66141891479492</v>
+        <v>2.66141939163208</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G925" t="n">
-        <v>2.66905355453491</v>
+        <v>2.66905403137207</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G926" t="n">
-        <v>2.67821550369263</v>
+        <v>2.67821502685547</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G931" t="n">
-        <v>2.79273438453674</v>
+        <v>2.79273390769958</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G932" t="n">
-        <v>2.76983046531677</v>
+        <v>2.76983022689819</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G934" t="n">
-        <v>2.76677656173706</v>
+        <v>2.76677632331848</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G935" t="n">
-        <v>2.79426121711731</v>
+        <v>2.79426097869873</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G936" t="n">
-        <v>2.76677656173706</v>
+        <v>2.76677632331848</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G939" t="n">
-        <v>2.68279552459717</v>
+        <v>2.68279576301575</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G940" t="n">
-        <v>2.67516136169434</v>
+        <v>2.67516112327576</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G941" t="n">
-        <v>2.7255494594574</v>
+        <v>2.72554993629456</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G942" t="n">
-        <v>2.69959211349487</v>
+        <v>2.69959187507629</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G944" t="n">
-        <v>2.72707676887512</v>
+        <v>2.72707653045654</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G945" t="n">
-        <v>2.78509950637817</v>
+        <v>2.78509926795959</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G947" t="n">
-        <v>2.78204560279846</v>
+        <v>2.78204584121704</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G950" t="n">
-        <v>2.82632637023926</v>
+        <v>2.82632613182068</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>2.89351058006287</v>
+        <v>2.89351081848145</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>2.8324339389801</v>
+        <v>2.83243417739868</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G959" t="n">
-        <v>2.89351058006287</v>
+        <v>2.89351081848145</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G960" t="n">
-        <v>2.87824130058289</v>
+        <v>2.87824153900146</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G962" t="n">
-        <v>2.87671422958374</v>
+        <v>2.87671446800232</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G964" t="n">
-        <v>2.89351058006287</v>
+        <v>2.89351081848145</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G966" t="n">
-        <v>2.85839176177979</v>
+        <v>2.85839152336121</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G968" t="n">
-        <v>2.87060713768005</v>
+        <v>2.87060689926147</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G970" t="n">
-        <v>2.84159541130066</v>
+        <v>2.84159564971924</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G971" t="n">
-        <v>2.87824130058289</v>
+        <v>2.87824153900146</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G972" t="n">
-        <v>2.86755299568176</v>
+        <v>2.86755323410034</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G973" t="n">
-        <v>2.87976861000061</v>
+        <v>2.87976837158203</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G975" t="n">
-        <v>2.91794157028198</v>
+        <v>2.9179413318634</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G976" t="n">
-        <v>2.93015646934509</v>
+        <v>2.93015670776367</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G978" t="n">
-        <v>2.94084525108337</v>
+        <v>2.94084548950195</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G979" t="n">
-        <v>2.902672290802</v>
+        <v>2.90267205238342</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G980" t="n">
-        <v>2.92557621002197</v>
+        <v>2.92557597160339</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G984" t="n">
-        <v>2.94389915466309</v>
+        <v>2.94389891624451</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G987" t="n">
-        <v>3.04009532928467</v>
+        <v>3.04009509086609</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G988" t="n">
-        <v>3.06299901008606</v>
+        <v>3.06299877166748</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G990" t="n">
-        <v>3.08284854888916</v>
+        <v>3.08284878730774</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>3.06147217750549</v>
+        <v>3.06147170066833</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>3.96799993515015</v>
       </c>
       <c r="G992" t="n">
-        <v>3.02940630912781</v>
+        <v>3.02940654754639</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G993" t="n">
-        <v>3.04620242118835</v>
+        <v>3.04620265960693</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G995" t="n">
-        <v>3.05078363418579</v>
+        <v>3.05078339576721</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G996" t="n">
-        <v>3.04162192344666</v>
+        <v>3.0416214466095</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G997" t="n">
-        <v>3.05689120292664</v>
+        <v>3.05689144134521</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.992760181427</v>
+        <v>2.99276065826416</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.94237232208252</v>
+        <v>2.94237208366394</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.97291040420532</v>
+        <v>2.97291088104248</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.98054504394531</v>
+        <v>2.98054528236389</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.93168354034424</v>
+        <v>2.93168377876282</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.99581432342529</v>
+        <v>2.99581408500671</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.03856778144836</v>
+        <v>3.03856801986694</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.08590221405029</v>
+        <v>3.08590245246887</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.0324604511261</v>
+        <v>3.03245997428894</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.98054504394531</v>
+        <v>2.98054528236389</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.94084525108337</v>
+        <v>2.94084548950195</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.94237232208252</v>
+        <v>2.94237208366394</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.95153331756592</v>
+        <v>2.9515335559845</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.05231022834778</v>
+        <v>3.0523099899292</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.04925608634949</v>
+        <v>3.04925632476807</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.00039529800415</v>
+        <v>3.00039505958557</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.04009532928467</v>
+        <v>3.04009509086609</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.13476395606995</v>
+        <v>3.13476371765137</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.23554062843323</v>
+        <v>3.23554015159607</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.17446374893188</v>
+        <v>3.17446351051331</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.13171029090881</v>
+        <v>3.13171052932739</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.13934469223022</v>
+        <v>3.13934445381165</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.19278693199158</v>
+        <v>3.192786693573</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.23095941543579</v>
+        <v>3.23095989227295</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.26607894897461</v>
+        <v>3.26607871055603</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.28287506103516</v>
+        <v>3.28287529945374</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.33173632621765</v>
+        <v>3.33173584938049</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.31188654899597</v>
+        <v>3.31188678741455</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.32410168647766</v>
+        <v>3.32410216331482</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.40655565261841</v>
+        <v>3.40655493736267</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.38823246955872</v>
+        <v>3.38823223114014</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.36838245391846</v>
+        <v>3.36838269233704</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.19889450073242</v>
+        <v>3.198894739151</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.16988301277161</v>
+        <v>3.16988277435303</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.14087128639221</v>
+        <v>3.14087152481079</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.04162192344666</v>
+        <v>3.0416214466095</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.13934469223022</v>
+        <v>3.13934445381165</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.12407565116882</v>
+        <v>3.12407541275024</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.71333408355713</v>
+        <v>2.71333432197571</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.57743835449219</v>
+        <v>2.57743859291077</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.36214280128479</v>
+        <v>2.36214303970337</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.35756206512451</v>
+        <v>2.35756230354309</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.47513484954834</v>
+        <v>2.4751353263855</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.3392391204834</v>
+        <v>2.33923935890198</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.36214280128479</v>
+        <v>2.36214303970337</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.51178097724915</v>
+        <v>2.51178121566772</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.4949848651886</v>
+        <v>2.49498462677002</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.42169284820557</v>
+        <v>2.42169308662415</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.44459652900696</v>
+        <v>2.44459676742554</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.35603523254395</v>
+        <v>2.35603547096252</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.46750092506409</v>
+        <v>2.46750044822693</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.45986580848694</v>
+        <v>2.45986533164978</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.44001603126526</v>
+        <v>2.44001626968384</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.43696188926697</v>
+        <v>2.43696212768555</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.49803900718689</v>
+        <v>2.49803876876831</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.51025414466858</v>
+        <v>2.51025438308716</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.41253137588501</v>
+        <v>2.41253161430359</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.49803900718689</v>
+        <v>2.49803876876831</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.47055435180664</v>
+        <v>2.47055411338806</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.46444654464722</v>
+        <v>2.4644467830658</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.41863894462585</v>
+        <v>2.41863918304443</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.41863894462585</v>
+        <v>2.41863918304443</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.48276948928833</v>
+        <v>2.48276972770691</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.45375776290894</v>
+        <v>2.45375823974609</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.35908889770508</v>
+        <v>2.35908913612366</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.19799995422363</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.44154286384583</v>
+        <v>2.44154262542725</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.54842710494995</v>
+        <v>2.54842686653137</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.63393449783325</v>
+        <v>2.63393473625183</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.63393449783325</v>
+        <v>2.63393473625183</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.72707676887512</v>
+        <v>2.72707653045654</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.7316575050354</v>
+        <v>2.73165702819824</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.65989208221436</v>
+        <v>2.65989232063293</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.68432259559631</v>
+        <v>2.68432283401489</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.65378451347351</v>
+        <v>2.65378427505493</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.65683841705322</v>
+        <v>2.65683817863464</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.45600008964539</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.63851547241211</v>
+        <v>2.63851523399353</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.52705025672913</v>
+        <v>2.52705001831055</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.54842710494995</v>
+        <v>2.54842686653137</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.5866003036499</v>
+        <v>2.58660006523132</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.61866545677185</v>
+        <v>2.61866521835327</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.61103081703186</v>
+        <v>2.61103057861328</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.62675952911377</v>
+        <v>2.62676000595093</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.58586406707764</v>
+        <v>2.58586430549622</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.60002064704895</v>
+        <v>2.60002040863037</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.5229480266571</v>
+        <v>2.52294778823853</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.5622706413269</v>
+        <v>2.56227016448975</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.52766633033752</v>
+        <v>2.5276665687561</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.53867673873901</v>
+        <v>2.53867697715759</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.58114552497864</v>
+        <v>2.58114528656006</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.61574935913086</v>
+        <v>2.61574959754944</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.6188952922821</v>
+        <v>2.61889553070068</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.6204686164856</v>
+        <v>2.62046837806702</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.54968690872192</v>
+        <v>2.54968738555908</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.52452087402344</v>
+        <v>2.52452063560486</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.58901023864746</v>
+        <v>2.58901000022888</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.5229480266571</v>
+        <v>2.52294778823853</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.50092744827271</v>
+        <v>2.50092720985413</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.48677110671997</v>
+        <v>2.48677086830139</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.47890639305115</v>
+        <v>2.47890615463257</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.25</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.55597901344299</v>
+        <v>2.55597877502441</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.66922831535339</v>
+        <v>2.66922855377197</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.61574935913086</v>
+        <v>2.61574959754944</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.55125999450684</v>
+        <v>2.55126023292542</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.63462448120117</v>
+        <v>2.63462424278259</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.25</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.55597901344299</v>
+        <v>2.55597877502441</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.57957243919373</v>
+        <v>2.5795726776123</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.52923941612244</v>
+        <v>2.52923965454102</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.55283331871033</v>
+        <v>2.55283308029175</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.54968690872192</v>
+        <v>2.54968738555908</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.5669891834259</v>
+        <v>2.56698942184448</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.59844756126404</v>
+        <v>2.59844732284546</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.5229480266571</v>
+        <v>2.52294778823853</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.52609372138977</v>
+        <v>2.52609348297119</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.51351046562195</v>
+        <v>2.51351070404053</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.51980185508728</v>
+        <v>2.51980209350586</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.47890639305115</v>
+        <v>2.47890615463257</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.43801093101501</v>
+        <v>2.43801069259644</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.40812540054321</v>
+        <v>2.40812563896179</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.39711475372314</v>
+        <v>2.39711499214172</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.32004237174988</v>
+        <v>2.32004261016846</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.2838659286499</v>
+        <v>2.28386545181274</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.31060457229614</v>
+        <v>2.3106050491333</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.27600073814392</v>
+        <v>2.2760009765625</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.21780323982239</v>
+        <v>2.21780347824097</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.19578266143799</v>
+        <v>2.19578289985657</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.14073038101196</v>
+        <v>2.14073085784912</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.12342858314514</v>
+        <v>2.12342882156372</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.20836591720581</v>
+        <v>2.20836615562439</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.35150051116943</v>
+        <v>2.35150074958801</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.32318806648254</v>
+        <v>2.32318830490112</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.34678196907043</v>
+        <v>2.34678173065186</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.38767743110657</v>
+        <v>2.38767766952515</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.37509417533875</v>
+        <v>2.37509441375732</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.45373964309692</v>
+        <v>2.4537398815155</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.40340685844421</v>
+        <v>2.40340638160706</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.38767743110657</v>
+        <v>2.38767766952515</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.39868783950806</v>
+        <v>2.39868807792664</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.37666726112366</v>
+        <v>2.37666702270508</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.41599011421204</v>
+        <v>2.41598987579346</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.40655255317688</v>
+        <v>2.4065523147583</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.38767743110657</v>
+        <v>2.38767766952515</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.3672297000885</v>
+        <v>2.36722946166992</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.36408424377441</v>
+        <v>2.36408376693726</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.26499056816101</v>
+        <v>2.26499080657959</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.29330253601074</v>
+        <v>2.29330277442932</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.34835505485535</v>
+        <v>2.34835481643677</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.32004237174988</v>
+        <v>2.32004261016846</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.24139714241028</v>
+        <v>2.2413969039917</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.28701138496399</v>
+        <v>2.28701114654541</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.31060457229614</v>
+        <v>2.3106050491333</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.34363627433777</v>
+        <v>2.34363579750061</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.40026092529297</v>
+        <v>2.40026068687439</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.38610458374023</v>
+        <v>2.38610434532166</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.36408424377441</v>
+        <v>2.36408376693726</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.43801093101501</v>
+        <v>2.43801069259644</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.48519802093506</v>
+        <v>2.48519825935364</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.40655255317688</v>
+        <v>2.4065523147583</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.39868783950806</v>
+        <v>2.39868807792664</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.35150051116943</v>
+        <v>2.35150074958801</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.2807195186615</v>
+        <v>2.28071975708008</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.87199997901917</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.2586989402771</v>
+        <v>2.25869870185852</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.23195934295654</v>
+        <v>2.23195958137512</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.2807195186615</v>
+        <v>2.28071975708008</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.44587540626526</v>
+        <v>2.44587516784668</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.41756248474121</v>
+        <v>2.41756296157837</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.44744825363159</v>
+        <v>2.44744849205017</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.45373964309692</v>
+        <v>2.4537398815155</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.48047947883606</v>
+        <v>2.48047924041748</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.43014574050903</v>
+        <v>2.43014597892761</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.3672297000885</v>
+        <v>2.36722946166992</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.34678196907043</v>
+        <v>2.34678173065186</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.32318806648254</v>
+        <v>2.32318830490112</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.37666726112366</v>
+        <v>2.37666702270508</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.30116772651672</v>
+        <v>2.30116748809814</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.40026092529297</v>
+        <v>2.40026068687439</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.42228150367737</v>
+        <v>2.42228126525879</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.44587540626526</v>
+        <v>2.44587516784668</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.44744825363159</v>
+        <v>2.44744849205017</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.48519802093506</v>
+        <v>2.48519825935364</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.50092744827271</v>
+        <v>2.50092720985413</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.45531249046326</v>
+        <v>2.45531272888184</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.43801093101501</v>
+        <v>2.43801069259644</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.49463534355164</v>
+        <v>2.49463558197021</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.57957243919373</v>
+        <v>2.5795726776123</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.61574935913086</v>
+        <v>2.61574959754944</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.6188952922821</v>
+        <v>2.61889553070068</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.58114552497864</v>
+        <v>2.58114528656006</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.25</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.55597901344299</v>
+        <v>2.55597877502441</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.58901023864746</v>
+        <v>2.58901000022888</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.60159349441528</v>
+        <v>2.6015932559967</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.59844756126404</v>
+        <v>2.59844732284546</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.56934857368469</v>
+        <v>2.56934881210327</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.60002064704895</v>
+        <v>2.60002040863037</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.61417627334595</v>
+        <v>2.61417651176453</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.30299997329712</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.597660779953</v>
+        <v>2.59766101837158</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.61732268333435</v>
+        <v>2.61732244491577</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.60159349441528</v>
+        <v>2.6015932559967</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.37299990653992</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.65271306037903</v>
+        <v>2.65271282196045</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.63855695724487</v>
+        <v>2.63855671882629</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.63462448120117</v>
+        <v>2.63462424278259</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.64012956619263</v>
+        <v>2.64012980461121</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1353" t="n">
-        <v>2.63069224357605</v>
+        <v>2.63069200515747</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.40300011634827</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.67630624771118</v>
+        <v>2.67630648612976</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.64642119407654</v>
+        <v>2.64642143249512</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.64012956619263</v>
+        <v>2.64012980461121</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.45700001716614</v>
       </c>
       <c r="G1359" t="n">
-        <v>2.71877503395081</v>
+        <v>2.71877527236938</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.37700009346008</v>
       </c>
       <c r="G1361" t="n">
-        <v>2.65585851669312</v>
+        <v>2.65585899353027</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.64799427986145</v>
+        <v>2.64799404144287</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.48699998855591</v>
       </c>
       <c r="G1364" t="n">
-        <v>2.74236869812012</v>
+        <v>2.7423689365387</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G1366" t="n">
-        <v>2.70383214950562</v>
+        <v>2.70383238792419</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G1368" t="n">
-        <v>2.75731158256531</v>
+        <v>2.75731134414673</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.51099991798401</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.76124358177185</v>
+        <v>2.76124382019043</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.74472832679749</v>
+        <v>2.74472784996033</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1373" t="n">
-        <v>2.74079585075378</v>
+        <v>2.74079561233521</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.52900004386902</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.77539992332458</v>
+        <v>2.77540016174316</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.8469672203064</v>
+        <v>2.84696698188782</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.87842559814453</v>
+        <v>2.87842535972595</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1385" t="n">
-        <v>2.89100885391235</v>
+        <v>2.89100909233093</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1387" t="n">
-        <v>2.8941547870636</v>
+        <v>2.89415502548218</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.52099990844727</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.76910853385925</v>
+        <v>2.76910829544067</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.77304077148438</v>
+        <v>2.7730405330658</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.7454400062561</v>
+        <v>2.74543976783752</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.46099996566772</v>
       </c>
       <c r="G1405" t="n">
-        <v>2.80957078933716</v>
+        <v>2.80957055091858</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.79901742935181</v>
+        <v>2.79901766777039</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G1407" t="n">
-        <v>2.77385258674622</v>
+        <v>2.77385234832764</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.77385258674622</v>
+        <v>2.77385234832764</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>3.52900004386902</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.86477160453796</v>
+        <v>2.86477184295654</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.87532472610474</v>
+        <v>2.87532496452332</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.90779614448547</v>
+        <v>2.90779638290405</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.96705603599548</v>
+        <v>2.96705627441406</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.01332759857178</v>
+        <v>3.0133273601532</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.02388072013855</v>
+        <v>3.02388048171997</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.75300002098083</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.0466103553772</v>
+        <v>3.04661059379578</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.06203436851501</v>
+        <v>3.06203413009644</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.7590000629425</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.05148124694824</v>
+        <v>3.05148100852966</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.95163226127625</v>
+        <v>2.95163202285767</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.90860772132874</v>
+        <v>2.90860795974731</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.65700006484985</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.96867966651917</v>
+        <v>2.96867942810059</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.59899997711182</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.92159652709961</v>
+        <v>2.92159628868103</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.63899993896484</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.95406770706177</v>
+        <v>2.95406746864319</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.63899993896484</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.95406770706177</v>
+        <v>2.95406746864319</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.9134783744812</v>
+        <v>2.91347861289978</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.95650267601013</v>
+        <v>2.95650291442871</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.95325565338135</v>
+        <v>2.95325589179993</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.6489999294281</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.96218538284302</v>
+        <v>2.96218514442444</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.90860772132874</v>
+        <v>2.90860795974731</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G1459" t="n">
-        <v>2.89643120765686</v>
+        <v>2.89643144607544</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.87045431137085</v>
+        <v>2.87045407295227</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.86964225769043</v>
+        <v>2.86964249610901</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.87776041030884</v>
+        <v>2.87776017189026</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.83635950088501</v>
+        <v>2.83635926246643</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1467" t="n">
-        <v>2.85990142822266</v>
+        <v>2.8599009513855</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.78927636146545</v>
+        <v>2.78927612304688</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.8290536403656</v>
+        <v>2.82905340194702</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.80145263671875</v>
+        <v>2.80145239830017</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.54299998283386</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.876136302948</v>
+        <v>2.87613654136658</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.56100010871887</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.89074897766113</v>
+        <v>2.89074873924255</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.88587784767151</v>
+        <v>2.88587808609009</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.95325565338135</v>
+        <v>2.95325589179993</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.96299695968628</v>
+        <v>2.96299719810486</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.95325565338135</v>
+        <v>2.95325589179993</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.60700011253357</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.92809081077576</v>
+        <v>2.92809057235718</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.9289026260376</v>
+        <v>2.92890238761902</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.65700006484985</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.96867966651917</v>
+        <v>2.96867942810059</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.94026708602905</v>
+        <v>2.94026732444763</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.94351410865784</v>
+        <v>2.94351434707642</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.90454912185669</v>
+        <v>2.90454888343811</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.90211343765259</v>
+        <v>2.90211367607117</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.73569846153259</v>
+        <v>2.73569869995117</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.38700008392334</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.74949908256531</v>
+        <v>2.74949932098389</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.83311223983765</v>
+        <v>2.83311200141907</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.76817011833191</v>
+        <v>2.76816987991333</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.77385258674622</v>
+        <v>2.77385234832764</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.51900005340576</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.85665392875671</v>
+        <v>2.85665369033813</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.88181900978088</v>
+        <v>2.8818187713623</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.87776041030884</v>
+        <v>2.87776017189026</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.89724326133728</v>
+        <v>2.8972430229187</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.91753745079041</v>
+        <v>2.91753768920898</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.78602910041809</v>
+        <v>2.78602886199951</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.44300007820129</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.79495882987976</v>
+        <v>2.79495859146118</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.9134783744812</v>
+        <v>2.91347861289978</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.94676160812378</v>
+        <v>2.94676184654236</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.00196242332458</v>
+        <v>3.00196266174316</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.62299990653992</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.94107890129089</v>
+        <v>2.94107913970947</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.3989999294281</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.75924015045166</v>
+        <v>2.75924038887024</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.46700000762939</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.81444120407104</v>
+        <v>2.81444144248962</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.80226469039917</v>
+        <v>2.80226445198059</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.40700006484985</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.76573467254639</v>
+        <v>2.76573443412781</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.7235221862793</v>
+        <v>2.72352194786072</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.34899997711182</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.71865153312683</v>
+        <v>2.71865129470825</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.69023871421814</v>
+        <v>2.69023895263672</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.73569846153259</v>
+        <v>2.73569869995117</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.81281781196594</v>
+        <v>2.81281733512878</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.67237973213196</v>
+        <v>2.67237997055054</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.64640307426453</v>
+        <v>2.64640283584595</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.59769630432129</v>
+        <v>2.59769606590271</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.65776753425598</v>
+        <v>2.65776777267456</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.75599336624146</v>
+        <v>2.75599312782288</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.73407530784607</v>
+        <v>2.73407506942749</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.73407530784607</v>
+        <v>2.73407506942749</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.76979327201843</v>
+        <v>2.76979351043701</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.67075610160828</v>
+        <v>2.67075634002686</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.73407530784607</v>
+        <v>2.73407506942749</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.73326349258423</v>
+        <v>2.73326301574707</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.73326349258423</v>
+        <v>2.73326301574707</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.95650267601013</v>
+        <v>2.95650291442871</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.91916084289551</v>
+        <v>2.91916060447693</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G1601" t="n">
-        <v>2.8785719871521</v>
+        <v>2.87857222557068</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.90454912185669</v>
+        <v>2.90454888343811</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.52099990844727</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.8582775592804</v>
+        <v>2.85827732086182</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.82824158668518</v>
+        <v>2.82824182510376</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.86071276664734</v>
+        <v>2.86071300506592</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.3529999256134</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.72189807891846</v>
+        <v>2.72189831733704</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.38100004196167</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.74462819099426</v>
+        <v>2.74462795257568</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.45700001716614</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.80632328987122</v>
+        <v>2.80632352828979</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.8290536403656</v>
+        <v>2.82905340194702</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.78927636146545</v>
+        <v>2.78927612304688</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.90454912185669</v>
+        <v>2.90454888343811</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.81281781196594</v>
+        <v>2.81281733512878</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.41100001335144</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.76898145675659</v>
+        <v>2.76898169517517</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.38299989700317</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.74625158309937</v>
+        <v>2.74625182151794</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.37700009346008</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.74138116836548</v>
+        <v>2.74138140678406</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.61230802536011</v>
+        <v>2.61230826377869</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.98699998855591</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.42478704452515</v>
+        <v>2.42478680610657</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.78099989891052</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.25756001472473</v>
+        <v>2.25756025314331</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.90100002288818</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.35497355461121</v>
+        <v>2.35497379302979</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.78299999237061</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.35837936401367</v>
+        <v>2.35837960243225</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.39397120475769</v>
+        <v>2.39397144317627</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.38295483589172</v>
+        <v>2.38295459747314</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.80900001525879</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.38041234016418</v>
+        <v>2.38041257858276</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.31177115440369</v>
+        <v>2.31177091598511</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.35414266586304</v>
+        <v>2.35414242744446</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.80900001525879</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.38041234016418</v>
+        <v>2.38041257858276</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.27533197402954</v>
+        <v>2.27533221244812</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.20753836631775</v>
+        <v>2.20753812789917</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.2778742313385</v>
+        <v>2.27787446975708</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.35414266586304</v>
+        <v>2.35414242744446</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.74699997901917</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.32787251472473</v>
+        <v>2.32787227630615</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.74699997901917</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.32787251472473</v>
+        <v>2.32787227630615</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>2.79299998283386</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.36685395240784</v>
+        <v>2.36685371398926</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.76099991798401</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.33973598480225</v>
+        <v>2.33973622322083</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.79099988937378</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.36515879631042</v>
+        <v>2.365159034729</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.37109112739563</v>
+        <v>2.37109088897705</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.76900005340576</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.34651589393616</v>
+        <v>2.34651565551758</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.33549928665161</v>
+        <v>2.33549904823303</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.33210945129395</v>
+        <v>2.33210921287537</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>2.73900008201599</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.32109308242798</v>
+        <v>2.3210928440094</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.30329704284668</v>
+        <v>2.3032968044281</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.25414657592773</v>
+        <v>2.25414633750916</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.42700004577637</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.05669665336609</v>
+        <v>2.05669689178467</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.03042650222778</v>
+        <v>2.03042674064636</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.01771521568298</v>
+        <v>2.01771545410156</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>2.34899997711182</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.99059784412384</v>
+        <v>1.99059760570526</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.98636090755463</v>
+        <v>1.98636066913605</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.95670068264008</v>
+        <v>1.95670092105865</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.89483916759491</v>
+        <v>1.89483892917633</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.90077090263367</v>
+        <v>1.90077066421509</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.83551907539368</v>
+        <v>1.83551919460297</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.85246801376343</v>
+        <v>1.85246789455414</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>2.26300001144409</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.91771924495697</v>
+        <v>1.91771948337555</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.74908196926117</v>
+        <v>1.74908185005188</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.75331914424896</v>
+        <v>1.75331926345825</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.80331718921661</v>
+        <v>1.8033173084259</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.78467381000519</v>
+        <v>1.7846736907959</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.09299993515015</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.77365732192993</v>
+        <v>1.77365720272064</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.91432964801788</v>
+        <v>1.91432976722717</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.03042650222778</v>
+        <v>2.03042674064636</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.03635859489441</v>
+        <v>2.03635883331299</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.04398536682129</v>
+        <v>2.04398512840271</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.05415463447571</v>
+        <v>2.05415439605713</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.0524594783783</v>
+        <v>2.05245995521545</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.08635663986206</v>
+        <v>2.08635640144348</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.13889694213867</v>
+        <v>2.13889670372009</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.57699990272522</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.18380999565125</v>
+        <v>2.18381023406982</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.18465757369995</v>
+        <v>2.18465781211853</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>2.63899993896484</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.23635053634644</v>
+        <v>2.23635077476501</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.22024917602539</v>
+        <v>2.22024941444397</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>2.64100003242493</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.23804545402527</v>
+        <v>2.23804521560669</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.63899993896484</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.23635053634644</v>
+        <v>2.23635077476501</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.3982081413269</v>
+        <v>2.39820837974548</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.35414266586304</v>
+        <v>2.35414242744446</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>2.55100011825562</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.16177725791931</v>
+        <v>2.16177749633789</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>2.56900000572205</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.17703080177307</v>
+        <v>2.17703056335449</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.13889694213867</v>
+        <v>2.13889670372009</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.14737105369568</v>
+        <v>2.1473708152771</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.11008429527283</v>
+        <v>2.11008453369141</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.1575403213501</v>
+        <v>2.15754008293152</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.51900005340576</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.13465976715088</v>
+        <v>2.13466000556946</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.1914370059967</v>
+        <v>2.19143724441528</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.2778742313385</v>
+        <v>2.27787446975708</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.23719787597656</v>
+        <v>2.23719811439514</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.34736275672913</v>
+        <v>2.34736299514771</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.32194042205811</v>
+        <v>2.32194018363953</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.32702469825745</v>
+        <v>2.32702493667603</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.28804349899292</v>
+        <v>2.2880437374115</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.65300011634827</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.24821448326111</v>
+        <v>2.24821424484253</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.30329704284668</v>
+        <v>2.3032968044281</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.19906401634216</v>
+        <v>2.19906377792358</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.20330095291138</v>
+        <v>2.2033007144928</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.1710991859436</v>
+        <v>2.17109894752502</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.12872791290283</v>
+        <v>2.12872767448425</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>2.52300000190735</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.13804936408997</v>
+        <v>2.13804912567139</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.48099994659424</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.10245728492737</v>
+        <v>2.10245752334595</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.11008429527283</v>
+        <v>2.11008453369141</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.38299989700317</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.01941013336182</v>
+        <v>2.01940989494324</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.42700004577637</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.05669665336609</v>
+        <v>2.05669689178467</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.39299988746643</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.02788424491882</v>
+        <v>2.0278844833374</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.0965256690979</v>
+        <v>2.09652543067932</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.11347389221191</v>
+        <v>2.11347413063049</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.52300000190735</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.13804936408997</v>
+        <v>2.13804912567139</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.14821863174438</v>
+        <v>2.14821839332581</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.1914370059967</v>
+        <v>2.19143724441528</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.20160603523254</v>
+        <v>2.20160627365112</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.2219443321228</v>
+        <v>2.22194409370422</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.2778742313385</v>
+        <v>2.27787446975708</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.36600613594055</v>
+        <v>2.36600637435913</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.39312386512756</v>
+        <v>2.39312362670898</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.4253261089325</v>
+        <v>2.42532587051392</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.51345801353455</v>
+        <v>2.51345825195312</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.99600005149841</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.53888082504272</v>
+        <v>2.5388810634613</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.56599855422974</v>
+        <v>2.56599831581116</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.52701711654663</v>
+        <v>2.52701687812805</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.51176285743713</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.4710865020752</v>
+        <v>2.47108674049377</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.47278141975403</v>
+        <v>2.47278165817261</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.4643075466156</v>
+        <v>2.46430730819702</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.44396948814392</v>
+        <v>2.44396924972534</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.42363119125366</v>
+        <v>2.42363095283508</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.46091794967651</v>
+        <v>2.46091771125793</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>3.49600005149841</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>4679733</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>3.49399995803833</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>3.53600001335144</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>
